--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.3.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00219_18600707.3" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.N_00219_18600707.3" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.3.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.3.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.3.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.N_00219_18600707.3" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00219_18600707.3" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y165"/>
+  <dimension ref="A1:Y168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -609,16 +609,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L54: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1,78 To Balance on hand from last year $ 48 14 cultivation. The lot extends to the Bay below â€”â€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L7: isolated marker/symbol line :: 400</t>
@@ -626,7 +630,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -677,7 +681,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -700,12 +704,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L73: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: |*% JOHN WHITEFORD, He â€”1-----------" â€”he â€” in will</t>
+          <t>L538: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 18. 2nd Ron Wolfstown 200 | who will be present in Montreal € n the occa-</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -782,17 +786,17 @@
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 1as (letter/digit mix) :: â€”1as will defy competition.</t>
+          <t>L63: suspicious token(s): 1as (letter/digit mix) :: —1as will defy competition.</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L179: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L179: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 1as (letter/digit mix) :: â€”1as will defy competition.</t>
+          <t>L539: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: 19. •. ** 200 sion; and the opportunity thus afforded to</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -814,7 +818,7 @@
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: |*% JOHN WHITEFORD, He â€”1-----------" â€”he â€” in will</t>
+          <t>L55: punctuation artifact: double/multiple hyphen :: |*% JOHN WHITEFORD, He —1-----------" —he — in will</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
@@ -842,12 +846,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>224</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>365</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -870,12 +874,12 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L248: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: pm â€¦</t>
+          <t>L307: stray/suspicious non-ASCII glyph(s): U+5730 CJK UNIFIED IDEOGRAPH-5730 | isolated marker/symbol line :: 地</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoine DÃ©lorier 2 toisestone.. - 12,00</t>
+          <t>L546: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: 98-• " 200 Establishments, will use every effort to make</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -897,7 +901,7 @@
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoine DÃ©lorier 2 toisestone.. - 12,00</t>
+          <t>L71: punctuation artifact: repeated periods :: Antoine Délorier 2 toisestone.. - 12,00</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
@@ -953,12 +957,12 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L301: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 14th â€œ</t>
+          <t>L356: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | punctuation artifact: repeated periods :: " Batisran ， at Batiscan...</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ,â€”"Wholesale and Retail.</t>
+          <t>L553: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN :: ±7, " " 200 on or before the 15th day of July, and all such</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -975,7 +979,7 @@
       </c>
       <c r="P6" s="1" t="inlineStr">
         <is>
-          <t>L356: punctuation artifact: repeated periods :: " Batisran ï¼Œ at Batiscan...</t>
+          <t>L356: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | punctuation artifact: repeated periods :: " Batisran ， at Batiscan...</t>
         </is>
       </c>
       <c r="Q6" s="1" t="inlineStr">
@@ -1020,7 +1024,7 @@
       <c r="E7" s="1" t="inlineStr"/>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>L480: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): Yamachiche27th (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Yamachieche at Yamachiche27th 28th Beaumier price of" vs "" :: " Yamachieche, at Yamachiche27th &amp; 28th â€œ</t>
+          <t>L480: suspicious token(s): Yamachiche27th (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Yamachieche at Yamachiche27th 28th Beaumier price of" vs "" :: " Yamachieche, at Yamachiche27th &amp; 28th “</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr"/>
@@ -1036,12 +1040,12 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L315: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 15th â€œ</t>
+          <t>L418: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: - â€” 1 sincere thanks to his friends and the</t>
+          <t>L554: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen :: • ----------------articles must be delivered at the Exhibition</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1058,7 +1062,7 @@
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
-          <t>L450: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: viere du Loup. â€¦ â€¦... 18th &amp; 19th â€œ</t>
+          <t>L450: punctuation artifact: repeated periods :: viere du Loup. … …... 18th &amp; 19th “</t>
         </is>
       </c>
       <c r="Q7" s="1" t="inlineStr">
@@ -1119,12 +1123,12 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L357: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 25th â€œ</t>
+          <t>L492: stray/suspicious non-ASCII glyph(s): U+516C CJK UNIFIED IDEOGRAPH-516C | isolated marker/symbol line :: 公</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L147: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: To Augustin Godin work â€”: 11,35</t>
+          <t>L640: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Apply •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -1141,7 +1145,7 @@
       </c>
       <c r="P8" s="1" t="inlineStr">
         <is>
-          <t>L464: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: at St. Lon. ... 21st &amp; 22nd â€œ</t>
+          <t>L464: punctuation artifact: repeated periods :: at St. Lon. ... 21st &amp; 22nd “</t>
         </is>
       </c>
       <c r="Q8" s="1" t="inlineStr">
@@ -1202,12 +1206,12 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L368: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 28th &amp; 29th â€œ</t>
+          <t>L500: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L172: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Salaries.........- â€” ......</t>
+          <t>L825: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1224,7 +1228,7 @@
       </c>
       <c r="P9" s="1" t="inlineStr">
         <is>
-          <t>L475: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: at S. Barnab...â€¦</t>
+          <t>L475: punctuation artifact: repeated periods :: at S. Barnab...…</t>
         </is>
       </c>
       <c r="Q9" s="1" t="inlineStr">
@@ -1257,12 +1261,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1285,12 +1289,12 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L394: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 4th â€œ</t>
+          <t>L571: stray/suspicious non-ASCII glyph(s): U+7F8E CJK UNIFIED IDEOGRAPH-7F8E | isolated marker/symbol line :: 美</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L193: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: rehantâ€™s Liquor Licence,.... 512,00</t>
+          <t>L872: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •• St. Stanislas and St. Tite,</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1345,7 +1349,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1368,12 +1372,12 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L403: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 5th â€œ</t>
+          <t>L631: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L196: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: dlarâ€™s Licence,..........13,00</t>
+          <t>L881: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Cash principle; and by this means will be•</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
@@ -1423,12 +1427,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>163</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>167</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1447,12 +1451,12 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L409: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 7th â€œ</t>
+          <t>L758: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1st July 1€60.</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L237: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paid to AimÃ© Panneton, for a Poll in</t>
+          <t>L914: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
@@ -1480,7 +1484,7 @@
       <c r="R12" s="1" t="inlineStr"/>
       <c r="S12" s="1" t="inlineStr">
         <is>
-          <t>L876: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------------------000 ----</t>
+          <t>L872: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •• St. Stanislas and St. Tite,</t>
         </is>
       </c>
       <c r="T12" s="1" t="inlineStr"/>
@@ -1507,7 +1511,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>163</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1526,19 +1530,19 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L450: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: viere du Loup. â€¦ â€¦... 18th &amp; 19th â€œ</t>
+          <t>L776: stray/suspicious non-ASCII glyph(s): U+7B49 CJK UNIFIED IDEOGRAPH-7B49 | isolated marker/symbol line :: 等</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L238: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: St. Philipâ€™s Ward, ......</t>
+          <t>L1134: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE :: ■ Olivier Pothier for the large</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L54: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
@@ -1559,7 +1563,7 @@
       <c r="R13" s="1" t="inlineStr"/>
       <c r="S13" s="1" t="inlineStr">
         <is>
-          <t>L934: punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: -* St. Narcisse, at St. Narcisse</t>
+          <t>L876: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------------------000 ----</t>
         </is>
       </c>
       <c r="T13" s="1" t="inlineStr"/>
@@ -1567,7 +1571,7 @@
       <c r="V13" s="1" t="inlineStr"/>
       <c r="W13" s="1" t="inlineStr">
         <is>
-          <t>L1351: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: Arriving in Montreal at â€” 6.30 P.M.</t>
+          <t>L1351: abbreviation/spacing may be garbled :: Arriving in Montreal at — 6.30 P.M.</t>
         </is>
       </c>
       <c r="X13" s="1" t="inlineStr"/>
@@ -1586,7 +1590,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1595,7 +1599,7 @@
       <c r="G14" s="1" t="inlineStr"/>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>L480: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): Yamachiche27th (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Yamachieche at Yamachiche27th 28th Beaumier price of" vs "" :: " Yamachieche, at Yamachiche27th &amp; 28th â€œ</t>
+          <t>L480: suspicious token(s): Yamachiche27th (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Yamachieche at Yamachiche27th 28th Beaumier price of" vs "" :: " Yamachieche, at Yamachiche27th &amp; 28th “</t>
         </is>
       </c>
       <c r="I14" s="1" t="inlineStr">
@@ -1605,12 +1609,12 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>L456: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: - St. LÃ©on, and Hunterstown,</t>
+          <t>L785: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: P: Prescription ， with full directions ree</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L251: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Jesuitsâ€™ Estates &amp; Crown Domain Branch,</t>
+          <t>L1242: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • VIEWS ON THE</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
@@ -1638,7 +1642,7 @@
       <c r="R14" s="1" t="inlineStr"/>
       <c r="S14" s="1" t="inlineStr">
         <is>
-          <t>L1017: line starts with punctuation glued to text :: ** St. Maurice, at St. Maurice</t>
+          <t>L934: punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: -* St. Narcisse, at St. Narcisse</t>
         </is>
       </c>
       <c r="T14" s="1" t="inlineStr"/>
@@ -1684,12 +1688,12 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>L464: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: at St. Lon. ... 21st &amp; 22nd â€œ</t>
+          <t>L796: stray/suspicious non-ASCII glyph(s): U+4FDD CJK UNIFIED IDEOGRAPH-4FDD | isolated marker/symbol line :: 保</t>
         </is>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>L302: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 200 â€”</t>
+          <t>L1509: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Maurice Sayer damage €</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr"/>
@@ -1713,7 +1717,7 @@
       <c r="R15" s="1" t="inlineStr"/>
       <c r="S15" s="1" t="inlineStr">
         <is>
-          <t>L1024: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | line starts with punctuation glued to text :: ** RiviÃ¨re du Loup, at</t>
+          <t>L1017: line starts with punctuation glued to text :: ** St. Maurice, at St. Maurice</t>
         </is>
       </c>
       <c r="T15" s="1" t="inlineStr"/>
@@ -1759,12 +1763,12 @@
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>L475: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: at S. Barnab...â€¦</t>
+          <t>L842: stray/suspicious non-ASCII glyph(s): U+5154 CJK UNIFIED IDEOGRAPH-5154 | isolated marker/symbol line :: 兔</t>
         </is>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>L342: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: rue. Esquireâ€™s barn, .</t>
+          <t>L1594: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr"/>
@@ -1788,7 +1792,7 @@
       <c r="R16" s="1" t="inlineStr"/>
       <c r="S16" s="1" t="inlineStr">
         <is>
-          <t>L1400: symbol-only separator/garbage line | line starts with punctuation glued to text :: ____1016,00</t>
+          <t>L1024: line starts with punctuation glued to text :: ** Rivière du Loup, at</t>
         </is>
       </c>
       <c r="T16" s="1" t="inlineStr"/>
@@ -1832,16 +1836,8 @@
           <t>L1240: suspicious token(s): IThree (odd internal casing) :: IThree Rivers, 28th June, 186 . 3-in.</t>
         </is>
       </c>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L476: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 25th &amp; 26th â€œ</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L367: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: I Quarter,.;.â€”</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
@@ -1863,7 +1859,7 @@
       <c r="R17" s="1" t="inlineStr"/>
       <c r="S17" s="1" t="inlineStr">
         <is>
-          <t>L1428: line starts with punctuation glued to text :: .secretary of the Municipality:</t>
+          <t>L1242: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • VIEWS ON THE</t>
         </is>
       </c>
       <c r="T17" s="1" t="inlineStr"/>
@@ -1895,16 +1891,8 @@
           <t>L1285: suspicious token(s): oClock (odd internal casing), meetingHer (odd internal casing), LieutenantBAINS (odd internal casing) :: [Sundays excepted.] at 7 oClock, meetingHer husband. LieutenantBAINS, was Secre-</t>
         </is>
       </c>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L480: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): Yamachiche27th (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Yamachieche at Yamachiche27th 28th Beaumier price of" vs "" :: " Yamachieche, at Yamachiche27th &amp; 28th â€œ</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L415: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: from Montreal on articles for Exhibitionâ€”</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
@@ -1926,7 +1914,7 @@
       <c r="R18" s="1" t="inlineStr"/>
       <c r="S18" s="1" t="inlineStr">
         <is>
-          <t>L1439: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----1 ?</t>
+          <t>L1400: symbol-only separator/garbage line | line starts with punctuation glued to text :: ____1016,00</t>
         </is>
       </c>
       <c r="T18" s="1" t="inlineStr"/>
@@ -1958,21 +1946,13 @@
           <t>L1291: suspicious token(s): 34ns (letter/digit mix) :: OREGON IF Three Envers. June 15, 1860, .34ns</t>
         </is>
       </c>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L489: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 29th â€œ</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L416: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: approved by the Local Committeesâ€”will be</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L73: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
@@ -1989,7 +1969,7 @@
       <c r="R19" s="1" t="inlineStr"/>
       <c r="S19" s="1" t="inlineStr">
         <is>
-          <t>L1586: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aFor (odd internal casing) :: aFor any further information, apply to</t>
+          <t>L1428: line starts with punctuation glued to text :: .secretary of the Municipality:</t>
         </is>
       </c>
       <c r="T19" s="1" t="inlineStr"/>
@@ -2017,16 +1997,8 @@
           <t>L1371: punctuation artifact: repeated periods | suspicious token(s): 00A (letter/digit mix) :: Arriving at Montreal at..7 00A.M.</t>
         </is>
       </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L492: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: å…¬</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L421: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: To G. Lanigan, Esq., .â€” 84.30</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
@@ -2048,7 +2020,7 @@
       <c r="R20" s="1" t="inlineStr"/>
       <c r="S20" s="1" t="inlineStr">
         <is>
-          <t>L1591: symbol-only separator/garbage line | line starts with punctuation glued to text :: *38</t>
+          <t>L1439: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----1 ?</t>
         </is>
       </c>
       <c r="T20" s="1" t="inlineStr"/>
@@ -2076,16 +2048,8 @@
           <t>L1418: suspicious token(s): LaBarre (odd internal casing) | abbreviation/spacing may be garbled :: To D.G. LaBarre Esq., (extracts)</t>
         </is>
       </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L500: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L475: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”|keeping, to examine, compare and stamp all</t>
-        </is>
-      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
@@ -2107,7 +2071,7 @@
       <c r="R21" s="1" t="inlineStr"/>
       <c r="S21" s="1" t="inlineStr">
         <is>
-          <t>L1657: line starts with punctuation glued to text | abbreviation/spacing may be garbled :: _____ Deputy C.C. C. Landrie, Charles</t>
+          <t>L1586: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aFor (odd internal casing) :: aFor any further information, apply to</t>
         </is>
       </c>
       <c r="T21" s="1" t="inlineStr"/>
@@ -2135,16 +2099,8 @@
           <t>L1434: punctuation artifact: repeated periods | suspicious token(s): ZephirinDuval (odd internal casing) :: I to ZephirinDuval.........</t>
         </is>
       </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L631: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L502: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Becancour and Ste. Gertrude,</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
@@ -2160,13 +2116,13 @@
       <c r="P22" s="1" t="inlineStr"/>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>L172: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Salaries.........- â€” ......</t>
+          <t>L172: punctuation artifact: repeated periods :: Salaries.........- — ......</t>
         </is>
       </c>
       <c r="R22" s="1" t="inlineStr"/>
       <c r="S22" s="1" t="inlineStr">
         <is>
-          <t>L1704: isolated marker/symbol line | line starts with punctuation glued to text :: .J</t>
+          <t>L1591: symbol-only separator/garbage line | line starts with punctuation glued to text :: *38</t>
         </is>
       </c>
       <c r="T22" s="1" t="inlineStr"/>
@@ -2194,16 +2150,8 @@
           <t>L1453: suspicious token(s): 1m (letter/digit mix) :: Three Rivers, June 15, 1860. 4-1m.</t>
         </is>
       </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L758: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: 1st July 1â‚¬60.</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L507: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Rivers Turf Club will be held at the Court.</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="inlineStr"/>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
@@ -2223,7 +2171,11 @@
         </is>
       </c>
       <c r="R23" s="1" t="inlineStr"/>
-      <c r="S23" s="1" t="inlineStr"/>
+      <c r="S23" s="1" t="inlineStr">
+        <is>
+          <t>L1657: line starts with punctuation glued to text | abbreviation/spacing may be garbled :: _____ Deputy C.C. C. Landrie, Charles</t>
+        </is>
+      </c>
       <c r="T23" s="1" t="inlineStr"/>
       <c r="U23" s="1" t="inlineStr"/>
       <c r="V23" s="1" t="inlineStr"/>
@@ -2249,16 +2201,8 @@
           <t>L1549: suspicious token(s): BACKl (odd internal casing) :: RACK. ROUND. BACKl. PUFF,</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>L776: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN | isolated marker/symbol line :: ç­‰</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L508: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: House on Monday next 9th inst, at 2 oâ€™clockI</t>
-        </is>
-      </c>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
@@ -2278,7 +2222,11 @@
         </is>
       </c>
       <c r="R24" s="1" t="inlineStr"/>
-      <c r="S24" s="1" t="inlineStr"/>
+      <c r="S24" s="1" t="inlineStr">
+        <is>
+          <t>L1704: isolated marker/symbol line | line starts with punctuation glued to text :: .J</t>
+        </is>
+      </c>
       <c r="T24" s="1" t="inlineStr"/>
       <c r="U24" s="1" t="inlineStr"/>
       <c r="V24" s="1" t="inlineStr"/>
@@ -2304,16 +2252,8 @@
           <t>L1580: suspicious token(s): DesChene (odd internal casing) :: :and DesChene Lakes, by the Steamers ** Pen-</t>
         </is>
       </c>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>L783: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: tiao " Oregon,â€� Snow Bird,"" Emerald."</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L538: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: 18. 2nd Ron Wolfstown 200 | who will be present in Montreal â‚¬ n the occa-</t>
-        </is>
-      </c>
+      <c r="J25" s="1" t="inlineStr"/>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
@@ -2359,16 +2299,8 @@
           <t>L1586: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aFor (odd internal casing) :: aFor any further information, apply to</t>
         </is>
       </c>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>L796: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ä¿�</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L539: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 19. â€¢. ** 200 sion; and the opportunity thus afforded to</t>
-        </is>
-      </c>
+      <c r="J26" s="1" t="inlineStr"/>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
@@ -2411,15 +2343,11 @@
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>L1587: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): AyImer (odd internal casing) :: the U. F. Coâ€™s: Office, AyImer, or on Board</t>
+          <t>L1587: suspicious token(s): AyImer (odd internal casing) :: the U. F. Co’s: Office, AyImer, or on Board</t>
         </is>
       </c>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L546: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 98-â€¢ " 200 Establishments, will use every effort to make</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
@@ -2466,11 +2394,7 @@
         </is>
       </c>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L553: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN :: Â±7, " " 200 on or before the 15th day of July, and all such</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
@@ -2513,11 +2437,7 @@
       </c>
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L554: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: â€¢ ----------------articles must be delivered at the Exhibition</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
@@ -2560,11 +2480,7 @@
       </c>
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L560: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SENGERSâ€”</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
@@ -2580,7 +2496,7 @@
       <c r="P30" s="1" t="inlineStr"/>
       <c r="Q30" s="1" t="inlineStr">
         <is>
-          <t>L193: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: rehantâ€™s Liquor Licence,.... 512,00</t>
+          <t>L193: punctuation artifact: repeated periods :: rehant’s Liquor Licence,.... 512,00</t>
         </is>
       </c>
       <c r="R30" s="1" t="inlineStr"/>
@@ -2607,11 +2523,7 @@
       </c>
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Arriving in Montreal,.........â€”7 A. M.</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
@@ -2621,13 +2533,13 @@
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L304: symbol-only separator/garbage line :: 20"</t>
+          <t>L302: symbol-only separator/garbage line :: 200 —</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
       <c r="Q31" s="1" t="inlineStr">
         <is>
-          <t>L194: punctuation artifact: repeated periods :: as Â« Rentes,.............58,66</t>
+          <t>L194: punctuation artifact: repeated periods :: as « Rentes,.............58,66</t>
         </is>
       </c>
       <c r="R31" s="1" t="inlineStr"/>
@@ -2654,11 +2566,7 @@
       </c>
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L640: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Apply â€¢</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
@@ -2668,7 +2576,7 @@
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L316: symbol-only separator/garbage line :: 14.00</t>
+          <t>L304: symbol-only separator/garbage line :: 20"</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -2701,11 +2609,7 @@
       </c>
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L646: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: Montreal, 10 April. 1860 â€˜84</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
@@ -2715,13 +2619,13 @@
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L318: symbol-only separator/garbage line :: 4-00</t>
+          <t>L316: symbol-only separator/garbage line :: 14.00</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
       <c r="Q33" s="1" t="inlineStr">
         <is>
-          <t>L196: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: dlarâ€™s Licence,..........13,00</t>
+          <t>L196: punctuation artifact: repeated periods :: dlar’s Licence,..........13,00</t>
         </is>
       </c>
       <c r="R33" s="1" t="inlineStr"/>
@@ -2748,11 +2652,7 @@
       </c>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L673: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: at station No. I, â€”..</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
@@ -2762,7 +2662,7 @@
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L320: symbol-only separator/garbage line :: 4.00</t>
+          <t>L318: symbol-only separator/garbage line :: 4-00</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2795,11 +2695,7 @@
       </c>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L717: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 5â€™0</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
@@ -2809,7 +2705,7 @@
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L322: symbol-only separator/garbage line :: 4.00</t>
+          <t>L320: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2842,11 +2738,7 @@
       </c>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L772: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 13th â€”</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
@@ -2856,7 +2748,7 @@
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L324: symbol-only separator/garbage line :: 4.00</t>
+          <t>L322: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2885,11 +2777,7 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L778: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: 4 Grande RiviÃ¨re, at the Ferry</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
@@ -2899,7 +2787,7 @@
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L326: symbol-only separator/garbage line :: $6375,09</t>
+          <t>L324: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2928,11 +2816,7 @@
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L825: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
@@ -2942,7 +2826,7 @@
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L350: isolated marker/symbol line :: 30</t>
+          <t>L326: symbol-only separator/garbage line :: $6375,09</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2971,11 +2855,7 @@
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L872: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢â€¢ St. Stanislas and St. Tite,</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
@@ -2985,7 +2865,7 @@
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L352: symbol-only separator/garbage line :: 31.00</t>
+          <t>L350: isolated marker/symbol line :: 30</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
@@ -3014,11 +2894,7 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L873: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: â€” at St. Stanislas.........28th &amp; 29th "</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
@@ -3028,7 +2904,7 @@
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L354: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 125,75</t>
+          <t>L352: symbol-only separator/garbage line :: 31.00</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
@@ -3057,11 +2933,7 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L881: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Cash principle; and by this means will beâ€¢</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
@@ -3071,7 +2943,7 @@
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L355: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...127.45</t>
+          <t>L354: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 125,75</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
@@ -3100,11 +2972,7 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L914: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
@@ -3114,7 +2982,7 @@
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L357: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 113.27</t>
+          <t>L355: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...127.45</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
@@ -3143,11 +3011,7 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L929: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 30th â€œ</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
@@ -3157,7 +3021,7 @@
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L359: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 125 15</t>
+          <t>L357: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 113.27</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
@@ -3186,11 +3050,7 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L931: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 4th â€œ</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
@@ -3200,7 +3060,7 @@
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L361: symbol-only separator/garbage line :: 491.62</t>
+          <t>L359: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 125 15</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
@@ -3229,11 +3089,7 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L947: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ing L E. Pacaudâ€™s insur</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
@@ -3243,7 +3099,7 @@
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L363: isolated marker/symbol line :: 70</t>
+          <t>L361: symbol-only separator/garbage line :: 491.62</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
@@ -3272,11 +3128,7 @@
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L965: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Expert Taxâ€™s occasion of</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
@@ -3286,7 +3138,7 @@
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L385: symbol-only separator/garbage line :: 75.00</t>
+          <t>L363: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr"/>
@@ -3315,11 +3167,7 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L966: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: the Governorâ€™s visit,....</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
@@ -3329,13 +3177,13 @@
       </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>L387: symbol-only separator/garbage line :: 18.80</t>
+          <t>L385: symbol-only separator/garbage line :: 75.00</t>
         </is>
       </c>
       <c r="P47" s="1" t="inlineStr"/>
       <c r="Q47" s="1" t="inlineStr">
         <is>
-          <t>L238: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: St. Philipâ€™s Ward, ......</t>
+          <t>L238: punctuation artifact: repeated periods :: St. Philip’s Ward, ......</t>
         </is>
       </c>
       <c r="R47" s="1" t="inlineStr"/>
@@ -3358,11 +3206,7 @@
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L975: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN :: â€˜or euregistration Doucetâ€™s</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
@@ -3372,7 +3216,7 @@
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>L397: isolated marker/symbol line :: h</t>
+          <t>L387: symbol-only separator/garbage line :: 18.80</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr"/>
@@ -3401,11 +3245,7 @@
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L992: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Canada, to the Writ of Sumn</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
@@ -3415,7 +3255,7 @@
       </c>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>L510: symbol-only separator/garbage line :: 10.00</t>
+          <t>L397: isolated marker/symbol line :: h</t>
         </is>
       </c>
       <c r="P49" s="1" t="inlineStr"/>
@@ -3444,11 +3284,7 @@
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L1007: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: strongâ€™s fire, â€”........</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
@@ -3458,7 +3294,7 @@
       </c>
       <c r="O50" s="1" t="inlineStr">
         <is>
-          <t>L512: isolated marker/symbol line :: 800</t>
+          <t>L510: symbol-only separator/garbage line :: 10.00</t>
         </is>
       </c>
       <c r="P50" s="1" t="inlineStr"/>
@@ -3487,11 +3323,7 @@
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L1019: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: a MaskinongÃ©, at MaskinongÃ©11th &amp;</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
@@ -3501,7 +3333,7 @@
       </c>
       <c r="O51" s="1" t="inlineStr">
         <is>
-          <t>L514: symbol-only separator/garbage line :: 4.00</t>
+          <t>L512: isolated marker/symbol line :: 800</t>
         </is>
       </c>
       <c r="P51" s="1" t="inlineStr"/>
@@ -3530,11 +3362,7 @@
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L1024: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | line starts with punctuation glued to text :: ** RiviÃ¨re du Loup, at</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
@@ -3544,7 +3372,7 @@
       </c>
       <c r="O52" s="1" t="inlineStr">
         <is>
-          <t>L516: symbol-only separator/garbage line :: 15.6)</t>
+          <t>L514: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="P52" s="1" t="inlineStr"/>
@@ -3573,11 +3401,7 @@
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L1028: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 44 St. LÃ©on, and Hunterstown,</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
@@ -3587,7 +3411,7 @@
       </c>
       <c r="O53" s="1" t="inlineStr">
         <is>
-          <t>L518: symbol-only separator/garbage line :: 91.30</t>
+          <t>L516: symbol-only separator/garbage line :: 15.6)</t>
         </is>
       </c>
       <c r="P53" s="1" t="inlineStr"/>
@@ -3616,11 +3440,7 @@
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L1029: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: at St. LÃ©on................ 21st &amp; 22nd "</t>
-        </is>
-      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
@@ -3630,7 +3450,7 @@
       </c>
       <c r="O54" s="1" t="inlineStr">
         <is>
-          <t>L528: symbol-only separator/garbage line :: 480.00</t>
+          <t>L518: symbol-only separator/garbage line :: 91.30</t>
         </is>
       </c>
       <c r="P54" s="1" t="inlineStr"/>
@@ -3659,11 +3479,7 @@
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L1031: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: " St. BarnabÃ© &amp; St. Paulin,</t>
-        </is>
-      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
@@ -3673,7 +3489,7 @@
       </c>
       <c r="O55" s="1" t="inlineStr">
         <is>
-          <t>L580: symbol-only separator/garbage line :: 8.00</t>
+          <t>L528: symbol-only separator/garbage line :: 480.00</t>
         </is>
       </c>
       <c r="P55" s="1" t="inlineStr"/>
@@ -3702,11 +3518,7 @@
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L1032: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: at St. BarnabÃ©............25th &amp; 26th "</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
@@ -3716,7 +3528,7 @@
       </c>
       <c r="O56" s="1" t="inlineStr">
         <is>
-          <t>L582: symbol-only separator/garbage line :: 5.00</t>
+          <t>L580: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="P56" s="1" t="inlineStr"/>
@@ -3745,11 +3557,7 @@
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L1046: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: a St Etienne, at St Etienne 6th â€œ</t>
-        </is>
-      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
@@ -3759,7 +3567,7 @@
       </c>
       <c r="O57" s="1" t="inlineStr">
         <is>
-          <t>L584: symbol-only separator/garbage line :: 8.00</t>
+          <t>L582: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="P57" s="1" t="inlineStr"/>
@@ -3788,11 +3596,7 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L1113: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Kiernanâ€™s Commercial Buildings,</t>
-        </is>
-      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
@@ -3802,7 +3606,7 @@
       </c>
       <c r="O58" s="1" t="inlineStr">
         <is>
-          <t>L586: symbol-only separator/garbage line :: $3842.404</t>
+          <t>L584: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="P58" s="1" t="inlineStr"/>
@@ -3831,21 +3635,17 @@
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
       <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L1171: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: follows:â€”</t>
-        </is>
-      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L179: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L179: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr">
         <is>
-          <t>L611: isolated marker/symbol line :: 9</t>
+          <t>L586: symbol-only separator/garbage line :: $3842.404</t>
         </is>
       </c>
       <c r="P59" s="1" t="inlineStr"/>
@@ -3874,11 +3674,7 @@
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
       <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L1228: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: N. B.â€”Any person or persons who neglects</t>
-        </is>
-      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
@@ -3888,7 +3684,7 @@
       </c>
       <c r="O60" s="1" t="inlineStr">
         <is>
-          <t>L613: symbol-only separator/garbage line :: 4 00</t>
+          <t>L611: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="P60" s="1" t="inlineStr"/>
@@ -3917,11 +3713,7 @@
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L1242: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ VIEWS ON THE</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
@@ -3931,7 +3723,7 @@
       </c>
       <c r="O61" s="1" t="inlineStr">
         <is>
-          <t>L614: isolated marker/symbol line :: 18</t>
+          <t>L613: symbol-only separator/garbage line :: 4 00</t>
         </is>
       </c>
       <c r="P61" s="1" t="inlineStr"/>
@@ -3960,11 +3752,7 @@
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L1282: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” CAPT. CUMING, 7 F MRS. FRANCIS PATTI BAINS, who</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
@@ -3974,7 +3762,7 @@
       </c>
       <c r="O62" s="1" t="inlineStr">
         <is>
-          <t>L616: symbol-only separator/garbage line :: 100.00</t>
+          <t>L614: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="P62" s="1" t="inlineStr"/>
@@ -4003,11 +3791,7 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L1286: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: steamer OREGON at Chattsâ€™ Railroad, and tary to General Platt in 1813. , GRECO</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
@@ -4017,7 +3801,7 @@
       </c>
       <c r="O63" s="1" t="inlineStr">
         <is>
-          <t>L627: symbol-only separator/garbage line :: 6.90</t>
+          <t>L616: symbol-only separator/garbage line :: 100.00</t>
         </is>
       </c>
       <c r="P63" s="1" t="inlineStr"/>
@@ -4046,11 +3830,7 @@
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L1290: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: - â€” Brooklyn, Long Island, N. Y. who will be</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
@@ -4060,7 +3840,7 @@
       </c>
       <c r="O64" s="1" t="inlineStr">
         <is>
-          <t>L642: symbol-only separator/garbage line :: 24.00</t>
+          <t>L627: symbol-only separator/garbage line :: 6.90</t>
         </is>
       </c>
       <c r="P64" s="1" t="inlineStr"/>
@@ -4089,11 +3869,7 @@
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr"/>
       <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L1351: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: Arriving in Montreal at â€” 6.30 P.M.</t>
-        </is>
-      </c>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
@@ -4103,7 +3879,7 @@
       </c>
       <c r="O65" s="1" t="inlineStr">
         <is>
-          <t>L687: isolated marker/symbol line :: 50</t>
+          <t>L642: symbol-only separator/garbage line :: 24.00</t>
         </is>
       </c>
       <c r="P65" s="1" t="inlineStr"/>
@@ -4132,11 +3908,7 @@
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr"/>
       <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L1420: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: To Mr. Charles DugrÃ© ........</t>
-        </is>
-      </c>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
@@ -4146,7 +3918,7 @@
       </c>
       <c r="O66" s="1" t="inlineStr">
         <is>
-          <t>L689: symbol-only separator/garbage line :: 4.05</t>
+          <t>L687: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="P66" s="1" t="inlineStr"/>
@@ -4175,11 +3947,7 @@
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
       <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L1430: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: I given to AimÃ© Panneton X ;</t>
-        </is>
-      </c>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
@@ -4189,7 +3957,7 @@
       </c>
       <c r="O67" s="1" t="inlineStr">
         <is>
-          <t>L710: symbol-only separator/garbage line :: 62.00</t>
+          <t>L689: symbol-only separator/garbage line :: 4.05</t>
         </is>
       </c>
       <c r="P67" s="1" t="inlineStr"/>
@@ -4218,11 +3986,7 @@
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr"/>
       <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L1436: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: ruing at 1 â€˜Clock [Sundays excepted,]</t>
-        </is>
-      </c>
+      <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
@@ -4232,7 +3996,7 @@
       </c>
       <c r="O68" s="1" t="inlineStr">
         <is>
-          <t>L712: isolated marker/symbol line :: 15</t>
+          <t>L710: symbol-only separator/garbage line :: 62.00</t>
         </is>
       </c>
       <c r="P68" s="1" t="inlineStr"/>
@@ -4261,11 +4025,7 @@
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr"/>
       <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L1466: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Chattâ€™s Railroad, and returning thence to</t>
-        </is>
-      </c>
+      <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
@@ -4275,7 +4035,7 @@
       </c>
       <c r="O69" s="1" t="inlineStr">
         <is>
-          <t>L714: symbol-only separator/garbage line :: 9.50</t>
+          <t>L712: isolated marker/symbol line :: 15</t>
         </is>
       </c>
       <c r="P69" s="1" t="inlineStr"/>
@@ -4304,11 +4064,7 @@
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr"/>
       <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L1478: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜HE SUBSCRIBER respectfully informs</t>
-        </is>
-      </c>
+      <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
@@ -4318,7 +4074,7 @@
       </c>
       <c r="O70" s="1" t="inlineStr">
         <is>
-          <t>L716: isolated marker/symbol line :: n</t>
+          <t>L714: symbol-only separator/garbage line :: 9.50</t>
         </is>
       </c>
       <c r="P70" s="1" t="inlineStr"/>
@@ -4347,11 +4103,7 @@
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr"/>
       <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L1509: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: Maurice Sayer damage â‚¬</t>
-        </is>
-      </c>
+      <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
@@ -4361,7 +4113,7 @@
       </c>
       <c r="O71" s="1" t="inlineStr">
         <is>
-          <t>L728: symbol-only separator/garbage line :: 4 50</t>
+          <t>L716: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="P71" s="1" t="inlineStr"/>
@@ -4390,11 +4142,7 @@
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr"/>
       <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L1561: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: HE Subscriber, for several years a restâ€”</t>
-        </is>
-      </c>
+      <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
@@ -4404,7 +4152,7 @@
       </c>
       <c r="O72" s="1" t="inlineStr">
         <is>
-          <t>L730: isolated marker/symbol line :: 37</t>
+          <t>L717: symbol-only separator/garbage line :: 5’0</t>
         </is>
       </c>
       <c r="P72" s="1" t="inlineStr"/>
@@ -4433,11 +4181,7 @@
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr"/>
       <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L1563: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: simple vegetable remedyâ€”a sure Cure for</t>
-        </is>
-      </c>
+      <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
@@ -4447,7 +4191,7 @@
       </c>
       <c r="O73" s="1" t="inlineStr">
         <is>
-          <t>L732: isolated marker/symbol line :: 90</t>
+          <t>L728: symbol-only separator/garbage line :: 4 50</t>
         </is>
       </c>
       <c r="P73" s="1" t="inlineStr"/>
@@ -4476,11 +4220,7 @@
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr"/>
       <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L1569: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜othose who desire it, he will send the</t>
-        </is>
-      </c>
+      <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
@@ -4490,7 +4230,7 @@
       </c>
       <c r="O74" s="1" t="inlineStr">
         <is>
-          <t>L749: isolated marker/symbol line :: A</t>
+          <t>L730: isolated marker/symbol line :: 37</t>
         </is>
       </c>
       <c r="P74" s="1" t="inlineStr"/>
@@ -4519,11 +4259,7 @@
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr"/>
       <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L1581: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | punctuation artifact: double/multiple hyphen :: tiae " -- Oregon,â€� 4- Snow Bird,â€� â€œ- Emerald,"</t>
-        </is>
-      </c>
+      <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
@@ -4533,7 +4269,7 @@
       </c>
       <c r="O75" s="1" t="inlineStr">
         <is>
-          <t>L751: symbol-only separator/garbage line :: 40.00</t>
+          <t>L732: isolated marker/symbol line :: 90</t>
         </is>
       </c>
       <c r="P75" s="1" t="inlineStr"/>
@@ -4562,11 +4298,7 @@
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr"/>
       <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L1582: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: and ** Anne Sisson,â€� either by the Hour, by</t>
-        </is>
-      </c>
+      <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
@@ -4576,7 +4308,7 @@
       </c>
       <c r="O76" s="1" t="inlineStr">
         <is>
-          <t>L760: symbol-only separator/garbage line :: 1.00</t>
+          <t>L749: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="P76" s="1" t="inlineStr"/>
@@ -4605,11 +4337,7 @@
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr"/>
       <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L1587: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): AyImer (odd internal casing) :: the U. F. Coâ€™s: Office, AyImer, or on Board</t>
-        </is>
-      </c>
+      <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
@@ -4619,7 +4347,7 @@
       </c>
       <c r="O77" s="1" t="inlineStr">
         <is>
-          <t>L762: isolated marker/symbol line :: 70</t>
+          <t>L751: symbol-only separator/garbage line :: 40.00</t>
         </is>
       </c>
       <c r="P77" s="1" t="inlineStr"/>
@@ -4648,11 +4376,7 @@
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr"/>
       <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L1594: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
@@ -4662,13 +4386,13 @@
       </c>
       <c r="O78" s="1" t="inlineStr">
         <is>
-          <t>L764: symbol-only separator/garbage line :: 16 00</t>
+          <t>L760: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="P78" s="1" t="inlineStr"/>
       <c r="Q78" s="1" t="inlineStr">
         <is>
-          <t>L554: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: â€¢ ----------------articles must be delivered at the Exhibition</t>
+          <t>L546: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: 98-• " 200 Establishments, will use every effort to make</t>
         </is>
       </c>
       <c r="R78" s="1" t="inlineStr"/>
@@ -4691,11 +4415,7 @@
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr"/>
       <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L1612: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: For M. Aaron Hart (RiviÃ¨re du</t>
-        </is>
-      </c>
+      <c r="K79" s="1" t="inlineStr"/>
       <c r="L79" s="1" t="inlineStr"/>
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
@@ -4705,13 +4425,13 @@
       </c>
       <c r="O79" s="1" t="inlineStr">
         <is>
-          <t>L766: symbol-only separator/garbage line :: 32.00</t>
+          <t>L762: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="P79" s="1" t="inlineStr"/>
       <c r="Q79" s="1" t="inlineStr">
         <is>
-          <t>L562: punctuation artifact: repeated periods :: Will leave POINT LEVI at..........6 P. M.</t>
+          <t>L554: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen :: • ----------------articles must be delivered at the Exhibition</t>
         </is>
       </c>
       <c r="R79" s="1" t="inlineStr"/>
@@ -4734,11 +4454,7 @@
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr"/>
       <c r="J80" s="1" t="inlineStr"/>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>L1621: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoine DÃ©lorier 4 do.. ....</t>
-        </is>
-      </c>
+      <c r="K80" s="1" t="inlineStr"/>
       <c r="L80" s="1" t="inlineStr"/>
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
@@ -4748,13 +4464,13 @@
       </c>
       <c r="O80" s="1" t="inlineStr">
         <is>
-          <t>L787: isolated marker/symbol line :: n</t>
+          <t>L764: symbol-only separator/garbage line :: 16 00</t>
         </is>
       </c>
       <c r="P80" s="1" t="inlineStr"/>
       <c r="Q80" s="1" t="inlineStr">
         <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Arriving in Montreal,.........â€”7 A. M.</t>
+          <t>L562: punctuation artifact: repeated periods :: Will leave POINT LEVI at..........6 P. M.</t>
         </is>
       </c>
       <c r="R80" s="1" t="inlineStr"/>
@@ -4777,11 +4493,7 @@
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr"/>
       <c r="J81" s="1" t="inlineStr"/>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>L1681: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: of Natureâ€™s simple herbs. Those desiring the</t>
-        </is>
-      </c>
+      <c r="K81" s="1" t="inlineStr"/>
       <c r="L81" s="1" t="inlineStr"/>
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
@@ -4791,13 +4503,13 @@
       </c>
       <c r="O81" s="1" t="inlineStr">
         <is>
-          <t>L798: symbol-only separator/garbage line :: 50.00</t>
+          <t>L766: symbol-only separator/garbage line :: 32.00</t>
         </is>
       </c>
       <c r="P81" s="1" t="inlineStr"/>
       <c r="Q81" s="1" t="inlineStr">
         <is>
-          <t>L567: punctuation artifact: repeated periods :: TREAL...................-......5 P. M.</t>
+          <t>L564: punctuation artifact: repeated periods :: Arriving in Montreal,.........—7 A. M.</t>
         </is>
       </c>
       <c r="R81" s="1" t="inlineStr"/>
@@ -4830,13 +4542,13 @@
       </c>
       <c r="O82" s="1" t="inlineStr">
         <is>
-          <t>L800: symbol-only separator/garbage line :: 3 37</t>
+          <t>L787: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="P82" s="1" t="inlineStr"/>
       <c r="Q82" s="1" t="inlineStr">
         <is>
-          <t>L569: punctuation artifact: double/multiple hyphen | abbreviation/spacing may be garbled :: Arriving at Point Levi, -------5:30 A.M.</t>
+          <t>L567: punctuation artifact: repeated periods :: TREAL...................-......5 P. M.</t>
         </is>
       </c>
       <c r="R82" s="1" t="inlineStr"/>
@@ -4864,18 +4576,18 @@
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L312: isolated marker/symbol line :: 337</t>
+          <t>L307: stray/suspicious non-ASCII glyph(s): U+5730 CJK UNIFIED IDEOGRAPH-5730 | isolated marker/symbol line :: 地</t>
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr">
         <is>
-          <t>L802: isolated marker/symbol line :: 36</t>
+          <t>L798: symbol-only separator/garbage line :: 50.00</t>
         </is>
       </c>
       <c r="P83" s="1" t="inlineStr"/>
       <c r="Q83" s="1" t="inlineStr">
         <is>
-          <t>L598: punctuation artifact: repeated periods :: Interest,..............</t>
+          <t>L569: punctuation artifact: double/multiple hyphen | abbreviation/spacing may be garbled :: Arriving at Point Levi, -------5:30 A.M.</t>
         </is>
       </c>
       <c r="R83" s="1" t="inlineStr"/>
@@ -4903,18 +4615,18 @@
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L318: isolated marker/symbol line :: 36</t>
+          <t>L312: isolated marker/symbol line :: 337</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr">
         <is>
-          <t>L825: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L800: symbol-only separator/garbage line :: 3 37</t>
         </is>
       </c>
       <c r="P84" s="1" t="inlineStr"/>
       <c r="Q84" s="1" t="inlineStr">
         <is>
-          <t>L606: punctuation artifact: repeated periods :: Costs. ............</t>
+          <t>L598: punctuation artifact: repeated periods :: Interest,..............</t>
         </is>
       </c>
       <c r="R84" s="1" t="inlineStr"/>
@@ -4942,18 +4654,18 @@
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L332: symbol-only separator/garbage line :: 1.30</t>
+          <t>L318: isolated marker/symbol line :: 36</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr">
         <is>
-          <t>L827: symbol-only separator/garbage line :: 1.25</t>
+          <t>L802: isolated marker/symbol line :: 36</t>
         </is>
       </c>
       <c r="P85" s="1" t="inlineStr"/>
       <c r="Q85" s="1" t="inlineStr">
         <is>
-          <t>L622: punctuation artifact: repeated periods :: the convenience of the purchasers..</t>
+          <t>L606: punctuation artifact: repeated periods :: Costs. ............</t>
         </is>
       </c>
       <c r="R85" s="1" t="inlineStr"/>
@@ -4981,18 +4693,18 @@
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L335: symbol-only separator/garbage line :: - 000</t>
+          <t>L332: symbol-only separator/garbage line :: 1.30</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr">
         <is>
-          <t>L829: symbol-only separator/garbage line :: 7.25</t>
+          <t>L825: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P86" s="1" t="inlineStr"/>
       <c r="Q86" s="1" t="inlineStr">
         <is>
-          <t>L649: punctuation artifact: repeated periods :: der, :........</t>
+          <t>L622: punctuation artifact: repeated periods :: the convenience of the purchasers..</t>
         </is>
       </c>
       <c r="R86" s="1" t="inlineStr"/>
@@ -5020,18 +4732,18 @@
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L337: symbol-only separator/garbage line :: 21.00</t>
+          <t>L335: symbol-only separator/garbage line :: - 000</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr">
         <is>
-          <t>L832: symbol-only separator/garbage line :: 2.00</t>
+          <t>L827: symbol-only separator/garbage line :: 1.25</t>
         </is>
       </c>
       <c r="P87" s="1" t="inlineStr"/>
       <c r="Q87" s="1" t="inlineStr">
         <is>
-          <t>L653: punctuation artifact: repeated periods; double/multiple hyphen :: Do. Do ..........-- .....</t>
+          <t>L649: punctuation artifact: repeated periods :: der, :........</t>
         </is>
       </c>
       <c r="R87" s="1" t="inlineStr"/>
@@ -5059,18 +4771,18 @@
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L341: isolated marker/symbol line :: O</t>
+          <t>L337: symbol-only separator/garbage line :: 21.00</t>
         </is>
       </c>
       <c r="O88" s="1" t="inlineStr">
         <is>
-          <t>L854: symbol-only separator/garbage line :: 5,21</t>
+          <t>L829: symbol-only separator/garbage line :: 7.25</t>
         </is>
       </c>
       <c r="P88" s="1" t="inlineStr"/>
       <c r="Q88" s="1" t="inlineStr">
         <is>
-          <t>L657: punctuation artifact: repeated periods :: No. 1 and No. 3, .......</t>
+          <t>L653: punctuation artifact: repeated periods; double/multiple hyphen :: Do. Do ..........-- .....</t>
         </is>
       </c>
       <c r="R88" s="1" t="inlineStr"/>
@@ -5098,18 +4810,18 @@
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L346: isolated marker/symbol line :: 89</t>
+          <t>L341: isolated marker/symbol line :: O</t>
         </is>
       </c>
       <c r="O89" s="1" t="inlineStr">
         <is>
-          <t>L856: symbol-only separator/garbage line :: 1.30</t>
+          <t>L832: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="P89" s="1" t="inlineStr"/>
       <c r="Q89" s="1" t="inlineStr">
         <is>
-          <t>L659: punctuation artifact: double/multiple hyphen :: For wood sawing, --------</t>
+          <t>L657: punctuation artifact: repeated periods :: No. 1 and No. 3, .......</t>
         </is>
       </c>
       <c r="R89" s="1" t="inlineStr"/>
@@ -5137,18 +4849,18 @@
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L361: symbol-only separator/garbage line :: 69.16</t>
+          <t>L346: isolated marker/symbol line :: 89</t>
         </is>
       </c>
       <c r="O90" s="1" t="inlineStr">
         <is>
-          <t>L858: symbol-only separator/garbage line :: 21 00</t>
+          <t>L854: symbol-only separator/garbage line :: 5,21</t>
         </is>
       </c>
       <c r="P90" s="1" t="inlineStr"/>
       <c r="Q90" s="1" t="inlineStr">
         <is>
-          <t>L673: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: at station No. I, â€”..</t>
+          <t>L659: punctuation artifact: double/multiple hyphen :: For wood sawing, --------</t>
         </is>
       </c>
       <c r="R90" s="1" t="inlineStr"/>
@@ -5176,18 +4888,18 @@
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L369: symbol-only separator/garbage line :: 0981</t>
+          <t>L361: symbol-only separator/garbage line :: 69.16</t>
         </is>
       </c>
       <c r="O91" s="1" t="inlineStr">
         <is>
-          <t>L876: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------------------000 ----</t>
+          <t>L856: symbol-only separator/garbage line :: 1.30</t>
         </is>
       </c>
       <c r="P91" s="1" t="inlineStr"/>
       <c r="Q91" s="1" t="inlineStr">
         <is>
-          <t>L755: punctuation artifact: repeated periods :: DSIN................Do</t>
+          <t>L673: punctuation artifact: repeated periods :: at station No. I, —..</t>
         </is>
       </c>
       <c r="R91" s="1" t="inlineStr"/>
@@ -5215,18 +4927,18 @@
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>L370: symbol-only separator/garbage line :: 1860</t>
+          <t>L369: symbol-only separator/garbage line :: 0981</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr">
         <is>
-          <t>L913: isolated marker/symbol line :: C</t>
+          <t>L858: symbol-only separator/garbage line :: 21 00</t>
         </is>
       </c>
       <c r="P92" s="1" t="inlineStr"/>
       <c r="Q92" s="1" t="inlineStr">
         <is>
-          <t>L781: punctuation artifact: repeated periods :: Celestin ...................</t>
+          <t>L755: punctuation artifact: repeated periods :: DSIN................Do</t>
         </is>
       </c>
       <c r="R92" s="1" t="inlineStr"/>
@@ -5254,18 +4966,18 @@
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
         <is>
-          <t>L373: symbol-only separator/garbage line :: 24.75</t>
+          <t>L370: symbol-only separator/garbage line :: 1860</t>
         </is>
       </c>
       <c r="O93" s="1" t="inlineStr">
         <is>
-          <t>L914: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L876: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------------------000 ----</t>
         </is>
       </c>
       <c r="P93" s="1" t="inlineStr"/>
       <c r="Q93" s="1" t="inlineStr">
         <is>
-          <t>L804: punctuation artifact: double/multiple hyphen :: ed, --------------------</t>
+          <t>L781: punctuation artifact: repeated periods :: Celestin ...................</t>
         </is>
       </c>
       <c r="R93" s="1" t="inlineStr"/>
@@ -5293,18 +5005,18 @@
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>L391: symbol-only separator/garbage line :: 4.50</t>
+          <t>L373: symbol-only separator/garbage line :: 24.75</t>
         </is>
       </c>
       <c r="O94" s="1" t="inlineStr">
         <is>
-          <t>L916: symbol-only separator/garbage line :: 16 00</t>
+          <t>L913: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P94" s="1" t="inlineStr"/>
       <c r="Q94" s="1" t="inlineStr">
         <is>
-          <t>L806: punctuation artifact: repeated periods :: Poli-hing of the stove......</t>
+          <t>L804: punctuation artifact: double/multiple hyphen :: ed, --------------------</t>
         </is>
       </c>
       <c r="R94" s="1" t="inlineStr"/>
@@ -5332,18 +5044,18 @@
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
         <is>
-          <t>L411: isolated marker/symbol line :: X</t>
+          <t>L391: symbol-only separator/garbage line :: 4.50</t>
         </is>
       </c>
       <c r="O95" s="1" t="inlineStr">
         <is>
-          <t>L918: symbol-only separator/garbage line :: 1.35</t>
+          <t>L914: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="P95" s="1" t="inlineStr"/>
       <c r="Q95" s="1" t="inlineStr">
         <is>
-          <t>L809: punctuation artifact: double/multiple hyphen :: whole year, ------------</t>
+          <t>L806: punctuation artifact: repeated periods :: Poli-hing of the stove......</t>
         </is>
       </c>
       <c r="R95" s="1" t="inlineStr"/>
@@ -5371,18 +5083,18 @@
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>L415: symbol-only separator/garbage line :: 35.00</t>
+          <t>L411: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O96" s="1" t="inlineStr">
         <is>
-          <t>L920: isolated marker/symbol line :: 00</t>
+          <t>L916: symbol-only separator/garbage line :: 16 00</t>
         </is>
       </c>
       <c r="P96" s="1" t="inlineStr"/>
       <c r="Q96" s="1" t="inlineStr">
         <is>
-          <t>L810: punctuation artifact: repeated periods :: Postage...................- -</t>
+          <t>L809: punctuation artifact: double/multiple hyphen :: whole year, ------------</t>
         </is>
       </c>
       <c r="R96" s="1" t="inlineStr"/>
@@ -5410,18 +5122,18 @@
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr">
         <is>
-          <t>L427: symbol-only separator/garbage line :: 3900</t>
+          <t>L415: symbol-only separator/garbage line :: 35.00</t>
         </is>
       </c>
       <c r="O97" s="1" t="inlineStr">
         <is>
-          <t>L921: isolated marker/symbol line :: C.</t>
+          <t>L918: symbol-only separator/garbage line :: 1.35</t>
         </is>
       </c>
       <c r="P97" s="1" t="inlineStr"/>
       <c r="Q97" s="1" t="inlineStr">
         <is>
-          <t>L819: punctuation artifact: repeated periods :: eil, ..................</t>
+          <t>L810: punctuation artifact: repeated periods :: Postage...................- -</t>
         </is>
       </c>
       <c r="R97" s="1" t="inlineStr"/>
@@ -5449,18 +5161,18 @@
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr">
         <is>
-          <t>L435: symbol-only separator/garbage line :: 39.00</t>
+          <t>L418: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="O98" s="1" t="inlineStr">
         <is>
-          <t>L998: isolated marker/symbol line :: C</t>
+          <t>L920: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="P98" s="1" t="inlineStr"/>
       <c r="Q98" s="1" t="inlineStr">
         <is>
-          <t>L866: punctuation artifact: repeated periods :: Anne ..................... 21st &amp; 22nd "</t>
+          <t>L819: punctuation artifact: repeated periods :: eil, ..................</t>
         </is>
       </c>
       <c r="R98" s="1" t="inlineStr"/>
@@ -5488,18 +5200,18 @@
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr">
         <is>
-          <t>L448: isolated marker/symbol line :: 30</t>
+          <t>L427: symbol-only separator/garbage line :: 3900</t>
         </is>
       </c>
       <c r="O99" s="1" t="inlineStr">
         <is>
-          <t>L1005: symbol-only separator/garbage line :: 1.00</t>
+          <t>L921: isolated marker/symbol line :: C.</t>
         </is>
       </c>
       <c r="P99" s="1" t="inlineStr"/>
       <c r="Q99" s="1" t="inlineStr">
         <is>
-          <t>L870: punctuation artifact: double/multiple hyphen :: " Batiscan, at Batiscan --25th "</t>
+          <t>L866: punctuation artifact: repeated periods :: Anne ..................... 21st &amp; 22nd "</t>
         </is>
       </c>
       <c r="R99" s="1" t="inlineStr"/>
@@ -5527,18 +5239,18 @@
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr">
         <is>
-          <t>L454: symbol-only separator/garbage line :: 1.60</t>
+          <t>L435: symbol-only separator/garbage line :: 39.00</t>
         </is>
       </c>
       <c r="O100" s="1" t="inlineStr">
         <is>
-          <t>L1052: isolated marker/symbol line :: 66</t>
+          <t>L998: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P100" s="1" t="inlineStr"/>
       <c r="Q100" s="1" t="inlineStr">
         <is>
-          <t>L873: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: â€” at St. Stanislas.........28th &amp; 29th "</t>
+          <t>L870: punctuation artifact: double/multiple hyphen :: " Batiscan, at Batiscan --25th "</t>
         </is>
       </c>
       <c r="R100" s="1" t="inlineStr"/>
@@ -5566,18 +5278,18 @@
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr">
         <is>
-          <t>L462: symbol-only separator/garbage line :: 7.87</t>
+          <t>L448: isolated marker/symbol line :: 30</t>
         </is>
       </c>
       <c r="O101" s="1" t="inlineStr">
         <is>
-          <t>L1054: isolated marker/symbol line :: 1"</t>
+          <t>L1005: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="P101" s="1" t="inlineStr"/>
       <c r="Q101" s="1" t="inlineStr">
         <is>
-          <t>L876: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------------------000 ----</t>
+          <t>L873: punctuation artifact: repeated periods :: — at St. Stanislas.........28th &amp; 29th "</t>
         </is>
       </c>
       <c r="R101" s="1" t="inlineStr"/>
@@ -5605,18 +5317,18 @@
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr">
         <is>
-          <t>L467: isolated marker/symbol line :: 77</t>
+          <t>L454: symbol-only separator/garbage line :: 1.60</t>
         </is>
       </c>
       <c r="O102" s="1" t="inlineStr">
         <is>
-          <t>L1056: symbol-only separator/garbage line :: 2,00</t>
+          <t>L1052: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="P102" s="1" t="inlineStr"/>
       <c r="Q102" s="1" t="inlineStr">
         <is>
-          <t>L934: punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: -* St. Narcisse, at St. Narcisse</t>
+          <t>L876: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------------------000 ----</t>
         </is>
       </c>
       <c r="R102" s="1" t="inlineStr"/>
@@ -5644,18 +5356,18 @@
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr">
         <is>
-          <t>L469: isolated marker/symbol line :: 1</t>
+          <t>L462: symbol-only separator/garbage line :: 7.87</t>
         </is>
       </c>
       <c r="O103" s="1" t="inlineStr">
         <is>
-          <t>L1058: symbol-only separator/garbage line :: 5.00</t>
+          <t>L1054: isolated marker/symbol line :: 1"</t>
         </is>
       </c>
       <c r="P103" s="1" t="inlineStr"/>
       <c r="Q103" s="1" t="inlineStr">
         <is>
-          <t>L935: punctuation artifact: double/multiple hyphen :: -- Champlain, at Champlain</t>
+          <t>L934: punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: -* St. Narcisse, at St. Narcisse</t>
         </is>
       </c>
       <c r="R103" s="1" t="inlineStr"/>
@@ -5683,18 +5395,18 @@
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr">
         <is>
-          <t>L478: isolated marker/symbol line :: Y</t>
+          <t>L467: isolated marker/symbol line :: 77</t>
         </is>
       </c>
       <c r="O104" s="1" t="inlineStr">
         <is>
-          <t>L1092: symbol-only separator/garbage line :: 9.00</t>
+          <t>L1056: symbol-only separator/garbage line :: 2,00</t>
         </is>
       </c>
       <c r="P104" s="1" t="inlineStr"/>
       <c r="Q104" s="1" t="inlineStr">
         <is>
-          <t>L938: punctuation artifact: repeated periods :: Cap de la Magdelaine..</t>
+          <t>L935: punctuation artifact: double/multiple hyphen :: -- Champlain, at Champlain</t>
         </is>
       </c>
       <c r="R104" s="1" t="inlineStr"/>
@@ -5722,18 +5434,18 @@
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr">
         <is>
-          <t>L485: isolated marker/symbol line :: 0</t>
+          <t>L469: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O105" s="1" t="inlineStr">
         <is>
-          <t>L1094: isolated marker/symbol line :: 39</t>
+          <t>L1058: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="P105" s="1" t="inlineStr"/>
       <c r="Q105" s="1" t="inlineStr">
         <is>
-          <t>L950: punctuation artifact: repeated periods :: Auditor for two years, ..</t>
+          <t>L938: punctuation artifact: repeated periods :: Cap de la Magdelaine..</t>
         </is>
       </c>
       <c r="R105" s="1" t="inlineStr"/>
@@ -5761,18 +5473,18 @@
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr">
         <is>
-          <t>L487: symbol-only separator/garbage line :: 1.00</t>
+          <t>L478: isolated marker/symbol line :: Y</t>
         </is>
       </c>
       <c r="O106" s="1" t="inlineStr">
         <is>
-          <t>L1095: symbol-only separator/garbage line :: 1.60</t>
+          <t>L1092: symbol-only separator/garbage line :: 9.00</t>
         </is>
       </c>
       <c r="P106" s="1" t="inlineStr"/>
       <c r="Q106" s="1" t="inlineStr">
         <is>
-          <t>L953: punctuation artifact: repeated periods :: ditor for two years,.....</t>
+          <t>L950: punctuation artifact: repeated periods :: Auditor for two years, ..</t>
         </is>
       </c>
       <c r="R106" s="1" t="inlineStr"/>
@@ -5800,18 +5512,18 @@
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr">
         <is>
-          <t>L492: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: å…¬</t>
+          <t>L485: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O107" s="1" t="inlineStr">
         <is>
-          <t>L1097: symbol-only separator/garbage line :: 7.87</t>
+          <t>L1094: isolated marker/symbol line :: 39</t>
         </is>
       </c>
       <c r="P107" s="1" t="inlineStr"/>
       <c r="Q107" s="1" t="inlineStr">
         <is>
-          <t>L958: punctuation artifact: repeated periods :: Hard ware, .............</t>
+          <t>L953: punctuation artifact: repeated periods :: ditor for two years,.....</t>
         </is>
       </c>
       <c r="R107" s="1" t="inlineStr"/>
@@ -5839,18 +5551,18 @@
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr">
         <is>
-          <t>L496: symbol-only separator/garbage line :: 618.60</t>
+          <t>L487: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="O108" s="1" t="inlineStr">
         <is>
-          <t>L1099: symbol-only separator/garbage line :: 4.80</t>
+          <t>L1095: symbol-only separator/garbage line :: 1.60</t>
         </is>
       </c>
       <c r="P108" s="1" t="inlineStr"/>
       <c r="Q108" s="1" t="inlineStr">
         <is>
-          <t>L960: punctuation artifact: repeated periods :: The Register office, ......</t>
+          <t>L958: punctuation artifact: repeated periods :: Hard ware, .............</t>
         </is>
       </c>
       <c r="R108" s="1" t="inlineStr"/>
@@ -5878,18 +5590,18 @@
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr">
         <is>
-          <t>L500: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L492: stray/suspicious non-ASCII glyph(s): U+516C CJK UNIFIED IDEOGRAPH-516C | isolated marker/symbol line :: 公</t>
         </is>
       </c>
       <c r="O109" s="1" t="inlineStr">
         <is>
-          <t>L1111: symbol-only separator/garbage line :: 334.31</t>
+          <t>L1097: symbol-only separator/garbage line :: 7.87</t>
         </is>
       </c>
       <c r="P109" s="1" t="inlineStr"/>
       <c r="Q109" s="1" t="inlineStr">
         <is>
-          <t>L962: punctuation artifact: repeated periods :: stall outside the hall.......</t>
+          <t>L960: punctuation artifact: repeated periods :: The Register office, ......</t>
         </is>
       </c>
       <c r="R109" s="1" t="inlineStr"/>
@@ -5917,18 +5629,18 @@
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr">
         <is>
-          <t>L503: isolated marker/symbol line :: S</t>
+          <t>L496: symbol-only separator/garbage line :: 618.60</t>
         </is>
       </c>
       <c r="O110" s="1" t="inlineStr">
         <is>
-          <t>L1135: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen :: ------</t>
+          <t>L1099: symbol-only separator/garbage line :: 4.80</t>
         </is>
       </c>
       <c r="P110" s="1" t="inlineStr"/>
       <c r="Q110" s="1" t="inlineStr">
         <is>
-          <t>L966: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: the Governorâ€™s visit,....</t>
+          <t>L962: punctuation artifact: repeated periods :: stall outside the hall.......</t>
         </is>
       </c>
       <c r="R110" s="1" t="inlineStr"/>
@@ -5956,18 +5668,18 @@
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr">
         <is>
-          <t>L504: isolated marker/symbol line :: 2</t>
+          <t>L500: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O111" s="1" t="inlineStr">
         <is>
-          <t>L1136: isolated marker/symbol line :: a-</t>
+          <t>L1111: symbol-only separator/garbage line :: 334.31</t>
         </is>
       </c>
       <c r="P111" s="1" t="inlineStr"/>
       <c r="Q111" s="1" t="inlineStr">
         <is>
-          <t>L972: punctuation artifact: repeated periods :: rendered, .............</t>
+          <t>L966: punctuation artifact: repeated periods :: the Governor’s visit,....</t>
         </is>
       </c>
       <c r="R111" s="1" t="inlineStr"/>
@@ -5995,18 +5707,18 @@
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr">
         <is>
-          <t>L508: isolated marker/symbol line :: t</t>
+          <t>L503: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O112" s="1" t="inlineStr">
         <is>
-          <t>L1138: isolated marker/symbol line :: 77</t>
+          <t>L1135: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen :: ------</t>
         </is>
       </c>
       <c r="P112" s="1" t="inlineStr"/>
       <c r="Q112" s="1" t="inlineStr">
         <is>
-          <t>L976: punctuation artifact: repeated periods :: obligation, - ...........</t>
+          <t>L972: punctuation artifact: repeated periods :: rendered, .............</t>
         </is>
       </c>
       <c r="R112" s="1" t="inlineStr"/>
@@ -6034,18 +5746,18 @@
       <c r="M113" s="1" t="inlineStr"/>
       <c r="N113" s="1" t="inlineStr">
         <is>
-          <t>L511: symbol-only separator/garbage line :: 182.25</t>
+          <t>L504: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O113" s="1" t="inlineStr">
         <is>
-          <t>L1140: symbol-only separator/garbage line :: 002 1/2</t>
+          <t>L1136: isolated marker/symbol line :: a-</t>
         </is>
       </c>
       <c r="P113" s="1" t="inlineStr"/>
       <c r="Q113" s="1" t="inlineStr">
         <is>
-          <t>L1007: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: strongâ€™s fire, â€”........</t>
+          <t>L976: punctuation artifact: repeated periods :: obligation, - ...........</t>
         </is>
       </c>
       <c r="R113" s="1" t="inlineStr"/>
@@ -6073,18 +5785,18 @@
       <c r="M114" s="1" t="inlineStr"/>
       <c r="N114" s="1" t="inlineStr">
         <is>
-          <t>L528: symbol-only separator/garbage line :: 114.00</t>
+          <t>L508: isolated marker/symbol line :: t</t>
         </is>
       </c>
       <c r="O114" s="1" t="inlineStr">
         <is>
-          <t>L1142: symbol-only separator/garbage line :: 7,05</t>
+          <t>L1138: isolated marker/symbol line :: 77</t>
         </is>
       </c>
       <c r="P114" s="1" t="inlineStr"/>
       <c r="Q114" s="1" t="inlineStr">
         <is>
-          <t>L1020: punctuation artifact: repeated periods :: as St. Justin, at St. Justin..</t>
+          <t>L1007: punctuation artifact: repeated periods :: strong’s fire, —........</t>
         </is>
       </c>
       <c r="R114" s="1" t="inlineStr"/>
@@ -6112,18 +5824,18 @@
       <c r="M115" s="1" t="inlineStr"/>
       <c r="N115" s="1" t="inlineStr">
         <is>
-          <t>L536: symbol-only separator/garbage line :: 51.00</t>
+          <t>L511: symbol-only separator/garbage line :: 182.25</t>
         </is>
       </c>
       <c r="O115" s="1" t="inlineStr">
         <is>
-          <t>L1144: symbol-only separator/garbage line :: 0,25</t>
+          <t>L1140: symbol-only separator/garbage line :: 002 1/2</t>
         </is>
       </c>
       <c r="P115" s="1" t="inlineStr"/>
       <c r="Q115" s="1" t="inlineStr">
         <is>
-          <t>L1026: punctuation artifact: repeated periods :: viere du Loop..........</t>
+          <t>L1020: punctuation artifact: repeated periods :: as St. Justin, at St. Justin..</t>
         </is>
       </c>
       <c r="R115" s="1" t="inlineStr"/>
@@ -6151,18 +5863,18 @@
       <c r="M116" s="1" t="inlineStr"/>
       <c r="N116" s="1" t="inlineStr">
         <is>
-          <t>L546: symbol-only separator/garbage line :: 1.39</t>
+          <t>L528: symbol-only separator/garbage line :: 114.00</t>
         </is>
       </c>
       <c r="O116" s="1" t="inlineStr">
         <is>
-          <t>L1158: symbol-only separator/garbage line :: - 1.00</t>
+          <t>L1142: symbol-only separator/garbage line :: 7,05</t>
         </is>
       </c>
       <c r="P116" s="1" t="inlineStr"/>
       <c r="Q116" s="1" t="inlineStr">
         <is>
-          <t>L1029: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: at St. LÃ©on................ 21st &amp; 22nd "</t>
+          <t>L1026: punctuation artifact: repeated periods :: viere du Loop..........</t>
         </is>
       </c>
       <c r="R116" s="1" t="inlineStr"/>
@@ -6190,18 +5902,18 @@
       <c r="M117" s="1" t="inlineStr"/>
       <c r="N117" s="1" t="inlineStr">
         <is>
-          <t>L549: isolated marker/symbol line :: B</t>
+          <t>L536: symbol-only separator/garbage line :: 51.00</t>
         </is>
       </c>
       <c r="O117" s="1" t="inlineStr">
         <is>
-          <t>L1190: isolated marker/symbol line :: -</t>
+          <t>L1144: symbol-only separator/garbage line :: 0,25</t>
         </is>
       </c>
       <c r="P117" s="1" t="inlineStr"/>
       <c r="Q117" s="1" t="inlineStr">
         <is>
-          <t>L1032: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: at St. BarnabÃ©............25th &amp; 26th "</t>
+          <t>L1029: punctuation artifact: repeated periods :: at St. Léon................ 21st &amp; 22nd "</t>
         </is>
       </c>
       <c r="R117" s="1" t="inlineStr"/>
@@ -6229,18 +5941,18 @@
       <c r="M118" s="1" t="inlineStr"/>
       <c r="N118" s="1" t="inlineStr">
         <is>
-          <t>L552: symbol-only separator/garbage line :: 4240</t>
+          <t>L546: symbol-only separator/garbage line :: 1.39</t>
         </is>
       </c>
       <c r="O118" s="1" t="inlineStr">
         <is>
-          <t>L1192: symbol-only separator/garbage line :: 618.60</t>
+          <t>L1158: symbol-only separator/garbage line :: - 1.00</t>
         </is>
       </c>
       <c r="P118" s="1" t="inlineStr"/>
       <c r="Q118" s="1" t="inlineStr">
         <is>
-          <t>L1036: punctuation artifact: double/multiple hyphen :: -- Pointe du Lac, at Pointe du</t>
+          <t>L1032: punctuation artifact: repeated periods :: at St. Barnabé............25th &amp; 26th "</t>
         </is>
       </c>
       <c r="R118" s="1" t="inlineStr"/>
@@ -6268,18 +5980,18 @@
       <c r="M119" s="1" t="inlineStr"/>
       <c r="N119" s="1" t="inlineStr">
         <is>
-          <t>L557: isolated marker/symbol line :: 5</t>
+          <t>L549: isolated marker/symbol line :: B</t>
         </is>
       </c>
       <c r="O119" s="1" t="inlineStr">
         <is>
-          <t>L1196: symbol-only separator/garbage line :: 5,38</t>
+          <t>L1190: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P119" s="1" t="inlineStr"/>
       <c r="Q119" s="1" t="inlineStr">
         <is>
-          <t>L1038: punctuation artifact: repeated periods :: Lac ...... 29th "</t>
+          <t>L1036: punctuation artifact: double/multiple hyphen :: -- Pointe du Lac, at Pointe du</t>
         </is>
       </c>
       <c r="R119" s="1" t="inlineStr"/>
@@ -6307,18 +6019,18 @@
       <c r="M120" s="1" t="inlineStr"/>
       <c r="N120" s="1" t="inlineStr">
         <is>
-          <t>L565: isolated marker/symbol line :: 9</t>
+          <t>L552: symbol-only separator/garbage line :: 4240</t>
         </is>
       </c>
       <c r="O120" s="1" t="inlineStr">
         <is>
-          <t>L1197: isolated marker/symbol line :: 5</t>
+          <t>L1192: symbol-only separator/garbage line :: 618.60</t>
         </is>
       </c>
       <c r="P120" s="1" t="inlineStr"/>
       <c r="Q120" s="1" t="inlineStr">
         <is>
-          <t>L1042: punctuation artifact: repeated periods :: 46 Ste. Flore, at Ste. Flore.. 4th "</t>
+          <t>L1038: punctuation artifact: repeated periods :: Lac ...... 29th "</t>
         </is>
       </c>
       <c r="R120" s="1" t="inlineStr"/>
@@ -6346,18 +6058,18 @@
       <c r="M121" s="1" t="inlineStr"/>
       <c r="N121" s="1" t="inlineStr">
         <is>
-          <t>L566: symbol-only separator/garbage line :: $1526.41</t>
+          <t>L557: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O121" s="1" t="inlineStr">
         <is>
-          <t>L1198: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 10,80</t>
+          <t>L1196: symbol-only separator/garbage line :: 5,38</t>
         </is>
       </c>
       <c r="P121" s="1" t="inlineStr"/>
       <c r="Q121" s="1" t="inlineStr">
         <is>
-          <t>L1135: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen :: ------</t>
+          <t>L1042: punctuation artifact: repeated periods :: 46 Ste. Flore, at Ste. Flore.. 4th "</t>
         </is>
       </c>
       <c r="R121" s="1" t="inlineStr"/>
@@ -6385,18 +6097,18 @@
       <c r="M122" s="1" t="inlineStr"/>
       <c r="N122" s="1" t="inlineStr">
         <is>
-          <t>L574: isolated marker/symbol line :: 3</t>
+          <t>L565: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O122" s="1" t="inlineStr">
         <is>
-          <t>L1218: symbol-only separator/garbage line :: 114.00</t>
+          <t>L1197: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="P122" s="1" t="inlineStr"/>
       <c r="Q122" s="1" t="inlineStr">
         <is>
-          <t>L1174: punctuation artifact: repeated periods | abbreviation/spacing may be garbled :: treal at ...............- - 10.30 A.M.</t>
+          <t>L1135: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen :: ------</t>
         </is>
       </c>
       <c r="R122" s="1" t="inlineStr"/>
@@ -6424,18 +6136,18 @@
       <c r="M123" s="1" t="inlineStr"/>
       <c r="N123" s="1" t="inlineStr">
         <is>
-          <t>L593: isolated marker/symbol line :: -</t>
+          <t>L566: symbol-only separator/garbage line :: $1526.41</t>
         </is>
       </c>
       <c r="O123" s="1" t="inlineStr">
         <is>
-          <t>L1220: symbol-only separator/garbage line :: 54.00</t>
+          <t>L1198: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 10,80</t>
         </is>
       </c>
       <c r="P123" s="1" t="inlineStr"/>
       <c r="Q123" s="1" t="inlineStr">
         <is>
-          <t>L1180: punctuation artifact: repeated periods :: mond) will leave Montreal at .. 5.00 P M.</t>
+          <t>L1174: punctuation artifact: repeated periods | abbreviation/spacing may be garbled :: treal at ...............- - 10.30 A.M.</t>
         </is>
       </c>
       <c r="R123" s="1" t="inlineStr"/>
@@ -6463,18 +6175,18 @@
       <c r="M124" s="1" t="inlineStr"/>
       <c r="N124" s="1" t="inlineStr">
         <is>
-          <t>L631: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L571: stray/suspicious non-ASCII glyph(s): U+7F8E CJK UNIFIED IDEOGRAPH-7F8E | isolated marker/symbol line :: 美</t>
         </is>
       </c>
       <c r="O124" s="1" t="inlineStr">
         <is>
-          <t>L1222: symbol-only separator/garbage line :: 1.39</t>
+          <t>L1218: symbol-only separator/garbage line :: 114.00</t>
         </is>
       </c>
       <c r="P124" s="1" t="inlineStr"/>
       <c r="Q124" s="1" t="inlineStr">
         <is>
-          <t>L1188: punctuation artifact: repeated periods :: Levi at.............-.,.-. 10.45 A M.</t>
+          <t>L1180: punctuation artifact: repeated periods :: mond) will leave Montreal at .. 5.00 P M.</t>
         </is>
       </c>
       <c r="R124" s="1" t="inlineStr"/>
@@ -6502,18 +6214,18 @@
       <c r="M125" s="1" t="inlineStr"/>
       <c r="N125" s="1" t="inlineStr">
         <is>
-          <t>L637: isolated marker/symbol line :: e.</t>
+          <t>L574: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O125" s="1" t="inlineStr">
         <is>
-          <t>L1224: isolated marker/symbol line :: 240</t>
+          <t>L1220: symbol-only separator/garbage line :: 54.00</t>
         </is>
       </c>
       <c r="P125" s="1" t="inlineStr"/>
       <c r="Q125" s="1" t="inlineStr">
         <is>
-          <t>L1198: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 10,80</t>
+          <t>L1188: punctuation artifact: repeated periods :: Levi at.............-.,.-. 10.45 A M.</t>
         </is>
       </c>
       <c r="R125" s="1" t="inlineStr"/>
@@ -6541,18 +6253,18 @@
       <c r="M126" s="1" t="inlineStr"/>
       <c r="N126" s="1" t="inlineStr">
         <is>
-          <t>L642: symbol-only separator/garbage line :: 523, 75</t>
+          <t>L593: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O126" s="1" t="inlineStr">
         <is>
-          <t>L1257: symbol-only separator/garbage line :: 5,00</t>
+          <t>L1222: symbol-only separator/garbage line :: 1.39</t>
         </is>
       </c>
       <c r="P126" s="1" t="inlineStr"/>
       <c r="Q126" s="1" t="inlineStr">
         <is>
-          <t>L1201: punctuation artifact: repeated periods :: Market................</t>
+          <t>L1198: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 10,80</t>
         </is>
       </c>
       <c r="R126" s="1" t="inlineStr"/>
@@ -6580,18 +6292,18 @@
       <c r="M127" s="1" t="inlineStr"/>
       <c r="N127" s="1" t="inlineStr">
         <is>
-          <t>L646: symbol-only separator/garbage line :: 1016, 00</t>
+          <t>L631: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O127" s="1" t="inlineStr">
         <is>
-          <t>L1259: symbol-only separator/garbage line :: 7.50</t>
+          <t>L1224: isolated marker/symbol line :: 240</t>
         </is>
       </c>
       <c r="P127" s="1" t="inlineStr"/>
       <c r="Q127" s="1" t="inlineStr">
         <is>
-          <t>L1247: punctuation artifact: repeated periods :: for stalls ...........</t>
+          <t>L1201: punctuation artifact: repeated periods :: Market................</t>
         </is>
       </c>
       <c r="R127" s="1" t="inlineStr"/>
@@ -6619,18 +6331,18 @@
       <c r="M128" s="1" t="inlineStr"/>
       <c r="N128" s="1" t="inlineStr">
         <is>
-          <t>L659: isolated marker/symbol line :: 1</t>
+          <t>L637: isolated marker/symbol line :: e.</t>
         </is>
       </c>
       <c r="O128" s="1" t="inlineStr">
         <is>
-          <t>L1260: symbol-only separator/garbage line :: 20,00</t>
+          <t>L1257: symbol-only separator/garbage line :: 5,00</t>
         </is>
       </c>
       <c r="P128" s="1" t="inlineStr"/>
       <c r="Q128" s="1" t="inlineStr">
         <is>
-          <t>L1249: punctuation artifact: repeated periods :: the large hall....</t>
+          <t>L1247: punctuation artifact: repeated periods :: for stalls ...........</t>
         </is>
       </c>
       <c r="R128" s="1" t="inlineStr"/>
@@ -6658,18 +6370,18 @@
       <c r="M129" s="1" t="inlineStr"/>
       <c r="N129" s="1" t="inlineStr">
         <is>
-          <t>L665: symbol-only separator/garbage line :: 167, 66</t>
+          <t>L642: symbol-only separator/garbage line :: 523, 75</t>
         </is>
       </c>
       <c r="O129" s="1" t="inlineStr">
         <is>
-          <t>L1262: symbol-only separator/garbage line :: 5,60</t>
+          <t>L1259: symbol-only separator/garbage line :: 7.50</t>
         </is>
       </c>
       <c r="P129" s="1" t="inlineStr"/>
       <c r="Q129" s="1" t="inlineStr">
         <is>
-          <t>L1298: punctuation artifact: repeated periods :: hall..</t>
+          <t>L1249: punctuation artifact: repeated periods :: the large hall....</t>
         </is>
       </c>
       <c r="R129" s="1" t="inlineStr"/>
@@ -6697,18 +6409,18 @@
       <c r="M130" s="1" t="inlineStr"/>
       <c r="N130" s="1" t="inlineStr">
         <is>
-          <t>L672: isolated marker/symbol line :: m</t>
+          <t>L646: symbol-only separator/garbage line :: 1016, 00</t>
         </is>
       </c>
       <c r="O130" s="1" t="inlineStr">
         <is>
-          <t>L1264: symbol-only separator/garbage line :: 2,50</t>
+          <t>L1260: symbol-only separator/garbage line :: 20,00</t>
         </is>
       </c>
       <c r="P130" s="1" t="inlineStr"/>
       <c r="Q130" s="1" t="inlineStr">
         <is>
-          <t>L1304: punctuation artifact: repeated periods :: Louis Sarazin for iron work...</t>
+          <t>L1298: punctuation artifact: repeated periods :: hall..</t>
         </is>
       </c>
       <c r="R130" s="1" t="inlineStr"/>
@@ -6736,18 +6448,18 @@
       <c r="M131" s="1" t="inlineStr"/>
       <c r="N131" s="1" t="inlineStr">
         <is>
-          <t>L677: isolated marker/symbol line :: X</t>
+          <t>L659: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O131" s="1" t="inlineStr">
         <is>
-          <t>L1266: symbol-only separator/garbage line :: 2,00</t>
+          <t>L1262: symbol-only separator/garbage line :: 5,60</t>
         </is>
       </c>
       <c r="P131" s="1" t="inlineStr"/>
       <c r="Q131" s="1" t="inlineStr">
         <is>
-          <t>L1306: punctuation artifact: repeated periods :: An accouunt for the little hall..</t>
+          <t>L1304: punctuation artifact: repeated periods :: Louis Sarazin for iron work...</t>
         </is>
       </c>
       <c r="R131" s="1" t="inlineStr"/>
@@ -6775,18 +6487,18 @@
       <c r="M132" s="1" t="inlineStr"/>
       <c r="N132" s="1" t="inlineStr">
         <is>
-          <t>L679: symbol-only separator/garbage line :: 34.48</t>
+          <t>L665: symbol-only separator/garbage line :: 167, 66</t>
         </is>
       </c>
       <c r="O132" s="1" t="inlineStr">
         <is>
-          <t>L1268: symbol-only separator/garbage line :: 1,12]</t>
+          <t>L1264: symbol-only separator/garbage line :: 2,50</t>
         </is>
       </c>
       <c r="P132" s="1" t="inlineStr"/>
       <c r="Q132" s="1" t="inlineStr">
         <is>
-          <t>L1308: punctuation artifact: repeated periods :: Mr. I ouis Lampron ........</t>
+          <t>L1306: punctuation artifact: repeated periods :: An accouunt for the little hall..</t>
         </is>
       </c>
       <c r="R132" s="1" t="inlineStr"/>
@@ -6814,18 +6526,18 @@
       <c r="M133" s="1" t="inlineStr"/>
       <c r="N133" s="1" t="inlineStr">
         <is>
-          <t>L680: isolated marker/symbol line :: 7</t>
+          <t>L672: isolated marker/symbol line :: m</t>
         </is>
       </c>
       <c r="O133" s="1" t="inlineStr">
         <is>
-          <t>L1270: symbol-only separator/garbage line :: 11.25</t>
+          <t>L1266: symbol-only separator/garbage line :: 2,00</t>
         </is>
       </c>
       <c r="P133" s="1" t="inlineStr"/>
       <c r="Q133" s="1" t="inlineStr">
         <is>
-          <t>L1340: punctuation artifact: repeated periods :: Louis Sarazin work.......</t>
+          <t>L1308: punctuation artifact: repeated periods :: Mr. I ouis Lampron ........</t>
         </is>
       </c>
       <c r="R133" s="1" t="inlineStr"/>
@@ -6853,18 +6565,18 @@
       <c r="M134" s="1" t="inlineStr"/>
       <c r="N134" s="1" t="inlineStr">
         <is>
-          <t>L687: symbol-only separator/garbage line :: 15, 13</t>
+          <t>L677: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O134" s="1" t="inlineStr">
         <is>
-          <t>L1272: symbol-only separator/garbage line :: 4,511</t>
+          <t>L1268: symbol-only separator/garbage line :: 1,12]</t>
         </is>
       </c>
       <c r="P134" s="1" t="inlineStr"/>
       <c r="Q134" s="1" t="inlineStr">
         <is>
-          <t>L1371: punctuation artifact: repeated periods | suspicious token(s): 00A (letter/digit mix) :: Arriving at Montreal at..7 00A.M.</t>
+          <t>L1340: punctuation artifact: repeated periods :: Louis Sarazin work.......</t>
         </is>
       </c>
       <c r="R134" s="1" t="inlineStr"/>
@@ -6892,18 +6604,18 @@
       <c r="M135" s="1" t="inlineStr"/>
       <c r="N135" s="1" t="inlineStr">
         <is>
-          <t>L697: symbol-only separator/garbage line :: 23.25</t>
+          <t>L679: symbol-only separator/garbage line :: 34.48</t>
         </is>
       </c>
       <c r="O135" s="1" t="inlineStr">
         <is>
-          <t>L1274: symbol-only separator/garbage line :: 12]</t>
+          <t>L1270: symbol-only separator/garbage line :: 11.25</t>
         </is>
       </c>
       <c r="P135" s="1" t="inlineStr"/>
       <c r="Q135" s="1" t="inlineStr">
         <is>
-          <t>L1398: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 523,75</t>
+          <t>L1371: punctuation artifact: repeated periods | suspicious token(s): 00A (letter/digit mix) :: Arriving at Montreal at..7 00A.M.</t>
         </is>
       </c>
       <c r="R135" s="1" t="inlineStr"/>
@@ -6931,18 +6643,18 @@
       <c r="M136" s="1" t="inlineStr"/>
       <c r="N136" s="1" t="inlineStr">
         <is>
-          <t>L704: symbol-only separator/garbage line :: 12.70</t>
+          <t>L680: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O136" s="1" t="inlineStr">
         <is>
-          <t>L1276: symbol-only separator/garbage line :: 7,10</t>
+          <t>L1272: symbol-only separator/garbage line :: 4,511</t>
         </is>
       </c>
       <c r="P136" s="1" t="inlineStr"/>
       <c r="Q136" s="1" t="inlineStr">
         <is>
-          <t>L1407: punctuation artifact: repeated periods :: Pompier............... .... 167,65</t>
+          <t>L1398: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 523,75</t>
         </is>
       </c>
       <c r="R136" s="1" t="inlineStr"/>
@@ -6970,18 +6682,18 @@
       <c r="M137" s="1" t="inlineStr"/>
       <c r="N137" s="1" t="inlineStr">
         <is>
-          <t>L709: symbol-only separator/garbage line :: 11, 37</t>
+          <t>L687: symbol-only separator/garbage line :: 15, 13</t>
         </is>
       </c>
       <c r="O137" s="1" t="inlineStr">
         <is>
-          <t>L1300: symbol-only separator/garbage line :: $1526.41</t>
+          <t>L1274: symbol-only separator/garbage line :: 12]</t>
         </is>
       </c>
       <c r="P137" s="1" t="inlineStr"/>
       <c r="Q137" s="1" t="inlineStr">
         <is>
-          <t>L1411: punctuation artifact: repeated periods :: To Mr. Louis Lampron .........</t>
+          <t>L1407: punctuation artifact: repeated periods :: Pompier............... .... 167,65</t>
         </is>
       </c>
       <c r="R137" s="1" t="inlineStr"/>
@@ -7009,18 +6721,18 @@
       <c r="M138" s="1" t="inlineStr"/>
       <c r="N138" s="1" t="inlineStr">
         <is>
-          <t>L717: symbol-only separator/garbage line :: 7.72</t>
+          <t>L697: symbol-only separator/garbage line :: 23.25</t>
         </is>
       </c>
       <c r="O138" s="1" t="inlineStr">
         <is>
-          <t>L1307: isolated marker/symbol line :: .</t>
+          <t>L1276: symbol-only separator/garbage line :: 7,10</t>
         </is>
       </c>
       <c r="P138" s="1" t="inlineStr"/>
       <c r="Q138" s="1" t="inlineStr">
         <is>
-          <t>L1413: punctuation artifact: repeated periods :: To William McDougall Esq......</t>
+          <t>L1411: punctuation artifact: repeated periods :: To Mr. Louis Lampron .........</t>
         </is>
       </c>
       <c r="R138" s="1" t="inlineStr"/>
@@ -7048,18 +6760,18 @@
       <c r="M139" s="1" t="inlineStr"/>
       <c r="N139" s="1" t="inlineStr">
         <is>
-          <t>L722: symbol-only separator/garbage line :: 140.00</t>
+          <t>L704: symbol-only separator/garbage line :: 12.70</t>
         </is>
       </c>
       <c r="O139" s="1" t="inlineStr">
         <is>
-          <t>L1349: isolated marker/symbol line :: :s</t>
+          <t>L1300: symbol-only separator/garbage line :: $1526.41</t>
         </is>
       </c>
       <c r="P139" s="1" t="inlineStr"/>
       <c r="Q139" s="1" t="inlineStr">
         <is>
-          <t>L1416: punctuation artifact: repeated periods :: tracts).......................</t>
+          <t>L1413: punctuation artifact: repeated periods :: To William McDougall Esq......</t>
         </is>
       </c>
       <c r="R139" s="1" t="inlineStr"/>
@@ -7087,18 +6799,18 @@
       <c r="M140" s="1" t="inlineStr"/>
       <c r="N140" s="1" t="inlineStr">
         <is>
-          <t>L726: symbol-only separator/garbage line :: 4.20</t>
+          <t>L709: symbol-only separator/garbage line :: 11, 37</t>
         </is>
       </c>
       <c r="O140" s="1" t="inlineStr">
         <is>
-          <t>L1359: symbol-only separator/garbage line :: $116,374</t>
+          <t>L1307: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="P140" s="1" t="inlineStr"/>
       <c r="Q140" s="1" t="inlineStr">
         <is>
-          <t>L1420: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: To Mr. Charles DugrÃ© ........</t>
+          <t>L1416: punctuation artifact: repeated periods :: tracts).......................</t>
         </is>
       </c>
       <c r="R140" s="1" t="inlineStr"/>
@@ -7126,18 +6838,18 @@
       <c r="M141" s="1" t="inlineStr"/>
       <c r="N141" s="1" t="inlineStr">
         <is>
-          <t>L734: isolated marker/symbol line :: T</t>
+          <t>L717: symbol-only separator/garbage line :: 7.72</t>
         </is>
       </c>
       <c r="O141" s="1" t="inlineStr">
         <is>
-          <t>L1363: isolated marker/symbol line :: 0</t>
+          <t>L1349: isolated marker/symbol line :: :s</t>
         </is>
       </c>
       <c r="P141" s="1" t="inlineStr"/>
       <c r="Q141" s="1" t="inlineStr">
         <is>
-          <t>L1422: punctuation artifact: repeated periods :: To Mr. Jos. Dufresne ........</t>
+          <t>L1420: punctuation artifact: repeated periods :: To Mr. Charles Dugré ........</t>
         </is>
       </c>
       <c r="R141" s="1" t="inlineStr"/>
@@ -7165,18 +6877,18 @@
       <c r="M142" s="1" t="inlineStr"/>
       <c r="N142" s="1" t="inlineStr">
         <is>
-          <t>L743: symbol-only separator/garbage line :: 2, 00</t>
+          <t>L722: symbol-only separator/garbage line :: 140.00</t>
         </is>
       </c>
       <c r="O142" s="1" t="inlineStr">
         <is>
-          <t>L1398: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 523,75</t>
+          <t>L1359: symbol-only separator/garbage line :: $116,374</t>
         </is>
       </c>
       <c r="P142" s="1" t="inlineStr"/>
       <c r="Q142" s="1" t="inlineStr">
         <is>
-          <t>L1424: punctuation artifact: repeated periods :: To Mr. Rowan, old account ....</t>
+          <t>L1422: punctuation artifact: repeated periods :: To Mr. Jos. Dufresne ........</t>
         </is>
       </c>
       <c r="R142" s="1" t="inlineStr"/>
@@ -7204,18 +6916,18 @@
       <c r="M143" s="1" t="inlineStr"/>
       <c r="N143" s="1" t="inlineStr">
         <is>
-          <t>L748: isolated marker/symbol line :: 1</t>
+          <t>L726: symbol-only separator/garbage line :: 4.20</t>
         </is>
       </c>
       <c r="O143" s="1" t="inlineStr">
         <is>
-          <t>L1400: symbol-only separator/garbage line | line starts with punctuation glued to text :: ____1016,00</t>
+          <t>L1363: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P143" s="1" t="inlineStr"/>
       <c r="Q143" s="1" t="inlineStr">
         <is>
-          <t>L1432: punctuation artifact: repeated periods :: I do. Louis Godin ........</t>
+          <t>L1424: punctuation artifact: repeated periods :: To Mr. Rowan, old account ....</t>
         </is>
       </c>
       <c r="R143" s="1" t="inlineStr"/>
@@ -7243,18 +6955,18 @@
       <c r="M144" s="1" t="inlineStr"/>
       <c r="N144" s="1" t="inlineStr">
         <is>
-          <t>L750: symbol-only separator/garbage line :: 2.85</t>
+          <t>L734: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O144" s="1" t="inlineStr">
         <is>
-          <t>L1439: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----1 ?</t>
+          <t>L1398: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 523,75</t>
         </is>
       </c>
       <c r="P144" s="1" t="inlineStr"/>
       <c r="Q144" s="1" t="inlineStr">
         <is>
-          <t>L1434: punctuation artifact: repeated periods | suspicious token(s): ZephirinDuval (odd internal casing) :: I to ZephirinDuval.........</t>
+          <t>L1432: punctuation artifact: repeated periods :: I do. Louis Godin ........</t>
         </is>
       </c>
       <c r="R144" s="1" t="inlineStr"/>
@@ -7282,18 +6994,18 @@
       <c r="M145" s="1" t="inlineStr"/>
       <c r="N145" s="1" t="inlineStr">
         <is>
-          <t>L754: isolated marker/symbol line :: 1</t>
+          <t>L743: symbol-only separator/garbage line :: 2, 00</t>
         </is>
       </c>
       <c r="O145" s="1" t="inlineStr">
         <is>
-          <t>L1490: isolated marker/symbol line :: 18</t>
+          <t>L1400: symbol-only separator/garbage line | line starts with punctuation glued to text :: ____1016,00</t>
         </is>
       </c>
       <c r="P145" s="1" t="inlineStr"/>
       <c r="Q145" s="1" t="inlineStr">
         <is>
-          <t>L1439: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----1 ?</t>
+          <t>L1434: punctuation artifact: repeated periods | suspicious token(s): ZephirinDuval (odd internal casing) :: I to ZephirinDuval.........</t>
         </is>
       </c>
       <c r="R145" s="1" t="inlineStr"/>
@@ -7321,18 +7033,18 @@
       <c r="M146" s="1" t="inlineStr"/>
       <c r="N146" s="1" t="inlineStr">
         <is>
-          <t>L756: isolated marker/symbol line :: 15</t>
+          <t>L748: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O146" s="1" t="inlineStr">
         <is>
-          <t>L1492: symbol-only separator/garbage line :: 5,30</t>
+          <t>L1439: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----1 ?</t>
         </is>
       </c>
       <c r="P146" s="1" t="inlineStr"/>
       <c r="Q146" s="1" t="inlineStr">
         <is>
-          <t>L1456: punctuation artifact: repeated periods :: winter roads ......</t>
+          <t>L1439: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----1 ?</t>
         </is>
       </c>
       <c r="R146" s="1" t="inlineStr"/>
@@ -7360,18 +7072,18 @@
       <c r="M147" s="1" t="inlineStr"/>
       <c r="N147" s="1" t="inlineStr">
         <is>
-          <t>L767: isolated marker/symbol line :: 2</t>
+          <t>L750: symbol-only separator/garbage line :: 2.85</t>
         </is>
       </c>
       <c r="O147" s="1" t="inlineStr">
         <is>
-          <t>L1513: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 20,00</t>
+          <t>L1490: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="P147" s="1" t="inlineStr"/>
       <c r="Q147" s="1" t="inlineStr">
         <is>
-          <t>L1458: punctuation artifact: repeated periods :: Louis Dargis .......</t>
+          <t>L1456: punctuation artifact: repeated periods :: winter roads ......</t>
         </is>
       </c>
       <c r="R147" s="1" t="inlineStr"/>
@@ -7399,18 +7111,18 @@
       <c r="M148" s="1" t="inlineStr"/>
       <c r="N148" s="1" t="inlineStr">
         <is>
-          <t>L771: symbol-only separator/garbage line :: 9, 60</t>
+          <t>L754: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O148" s="1" t="inlineStr">
         <is>
-          <t>L1514: isolated marker/symbol line :: - 4</t>
+          <t>L1492: symbol-only separator/garbage line :: 5,30</t>
         </is>
       </c>
       <c r="P148" s="1" t="inlineStr"/>
       <c r="Q148" s="1" t="inlineStr">
         <is>
-          <t>L1503: punctuation artifact: repeated periods :: rent lot......</t>
+          <t>L1458: punctuation artifact: repeated periods :: Louis Dargis .......</t>
         </is>
       </c>
       <c r="R148" s="1" t="inlineStr"/>
@@ -7438,18 +7150,18 @@
       <c r="M149" s="1" t="inlineStr"/>
       <c r="N149" s="1" t="inlineStr">
         <is>
-          <t>L776: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN | isolated marker/symbol line :: ç­‰</t>
+          <t>L756: isolated marker/symbol line :: 15</t>
         </is>
       </c>
       <c r="O149" s="1" t="inlineStr">
         <is>
-          <t>L1516: symbol-only separator/garbage line :: 11,37</t>
+          <t>L1513: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 20,00</t>
         </is>
       </c>
       <c r="P149" s="1" t="inlineStr"/>
       <c r="Q149" s="1" t="inlineStr">
         <is>
-          <t>L1507: punctuation artifact: repeated periods :: sioner Street. .......</t>
+          <t>L1503: punctuation artifact: repeated periods :: rent lot......</t>
         </is>
       </c>
       <c r="R149" s="1" t="inlineStr"/>
@@ -7477,18 +7189,18 @@
       <c r="M150" s="1" t="inlineStr"/>
       <c r="N150" s="1" t="inlineStr">
         <is>
-          <t>L779: symbol-only separator/garbage line :: 53, 80</t>
+          <t>L767: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O150" s="1" t="inlineStr">
         <is>
-          <t>L1518: symbol-only separator/garbage line :: 7,72</t>
+          <t>L1514: isolated marker/symbol line :: - 4</t>
         </is>
       </c>
       <c r="P150" s="1" t="inlineStr"/>
       <c r="Q150" s="1" t="inlineStr">
         <is>
-          <t>L1513: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 20,00</t>
+          <t>L1507: punctuation artifact: repeated periods :: sioner Street. .......</t>
         </is>
       </c>
       <c r="R150" s="1" t="inlineStr"/>
@@ -7516,18 +7228,18 @@
       <c r="M151" s="1" t="inlineStr"/>
       <c r="N151" s="1" t="inlineStr">
         <is>
-          <t>L796: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ä¿�</t>
+          <t>L771: symbol-only separator/garbage line :: 9, 60</t>
         </is>
       </c>
       <c r="O151" s="1" t="inlineStr">
         <is>
-          <t>L1520: symbol-only separator/garbage line :: 140,00</t>
+          <t>L1516: symbol-only separator/garbage line :: 11,37</t>
         </is>
       </c>
       <c r="P151" s="1" t="inlineStr"/>
       <c r="Q151" s="1" t="inlineStr">
         <is>
-          <t>L1557: punctuation artifact: repeated periods :: &amp;c., &amp;c., &amp;c..</t>
+          <t>L1513: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 20,00</t>
         </is>
       </c>
       <c r="R151" s="1" t="inlineStr"/>
@@ -7555,18 +7267,18 @@
       <c r="M152" s="1" t="inlineStr"/>
       <c r="N152" s="1" t="inlineStr">
         <is>
-          <t>L801: symbol-only separator/garbage line :: 61, 67</t>
+          <t>L776: stray/suspicious non-ASCII glyph(s): U+7B49 CJK UNIFIED IDEOGRAPH-7B49 | isolated marker/symbol line :: 等</t>
         </is>
       </c>
       <c r="O152" s="1" t="inlineStr">
         <is>
-          <t>L1522: symbol-only separator/garbage line :: 4,20</t>
+          <t>L1518: symbol-only separator/garbage line :: 7,72</t>
         </is>
       </c>
       <c r="P152" s="1" t="inlineStr"/>
       <c r="Q152" s="1" t="inlineStr">
         <is>
-          <t>L1581: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | punctuation artifact: double/multiple hyphen :: tiae " -- Oregon,â€� 4- Snow Bird,â€� â€œ- Emerald,"</t>
+          <t>L1557: punctuation artifact: repeated periods :: &amp;c., &amp;c., &amp;c..</t>
         </is>
       </c>
       <c r="R152" s="1" t="inlineStr"/>
@@ -7594,18 +7306,18 @@
       <c r="M153" s="1" t="inlineStr"/>
       <c r="N153" s="1" t="inlineStr">
         <is>
-          <t>L814: isolated marker/symbol line :: 2</t>
+          <t>L779: symbol-only separator/garbage line :: 53, 80</t>
         </is>
       </c>
       <c r="O153" s="1" t="inlineStr">
         <is>
-          <t>L1524: isolated marker/symbol line :: I</t>
+          <t>L1520: symbol-only separator/garbage line :: 140,00</t>
         </is>
       </c>
       <c r="P153" s="1" t="inlineStr"/>
       <c r="Q153" s="1" t="inlineStr">
         <is>
-          <t>L1601: punctuation artifact: repeated periods :: Coteau..............****......</t>
+          <t>L1581: punctuation artifact: double/multiple hyphen :: tiae " -- Oregon,” 4- Snow Bird,” “- Emerald,"</t>
         </is>
       </c>
       <c r="R153" s="1" t="inlineStr"/>
@@ -7633,18 +7345,18 @@
       <c r="M154" s="1" t="inlineStr"/>
       <c r="N154" s="1" t="inlineStr">
         <is>
-          <t>L815: isolated marker/symbol line :: S</t>
+          <t>L796: stray/suspicious non-ASCII glyph(s): U+4FDD CJK UNIFIED IDEOGRAPH-4FDD | isolated marker/symbol line :: 保</t>
         </is>
       </c>
       <c r="O154" s="1" t="inlineStr">
         <is>
-          <t>L1590: isolated marker/symbol line :: :</t>
+          <t>L1522: symbol-only separator/garbage line :: 4,20</t>
         </is>
       </c>
       <c r="P154" s="1" t="inlineStr"/>
       <c r="Q154" s="1" t="inlineStr">
         <is>
-          <t>L1607: punctuation artifact: repeated periods :: The Inspector .................</t>
+          <t>L1601: punctuation artifact: repeated periods :: Coteau..............****......</t>
         </is>
       </c>
       <c r="R154" s="1" t="inlineStr"/>
@@ -7672,18 +7384,18 @@
       <c r="M155" s="1" t="inlineStr"/>
       <c r="N155" s="1" t="inlineStr">
         <is>
-          <t>L825: symbol-only separator/garbage line :: 618, 60</t>
+          <t>L801: symbol-only separator/garbage line :: 61, 67</t>
         </is>
       </c>
       <c r="O155" s="1" t="inlineStr">
         <is>
-          <t>L1591: symbol-only separator/garbage line | line starts with punctuation glued to text :: *38</t>
+          <t>L1524: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P155" s="1" t="inlineStr"/>
       <c r="Q155" s="1" t="inlineStr">
         <is>
-          <t>L1609: punctuation artifact: repeated periods :: . Joseph Panneton winter roads..</t>
+          <t>L1607: punctuation artifact: repeated periods :: The Inspector .................</t>
         </is>
       </c>
       <c r="R155" s="1" t="inlineStr"/>
@@ -7711,18 +7423,18 @@
       <c r="M156" s="1" t="inlineStr"/>
       <c r="N156" s="1" t="inlineStr">
         <is>
-          <t>L834: isolated marker/symbol line :: 4</t>
+          <t>L814: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O156" s="1" t="inlineStr">
         <is>
-          <t>L1593: isolated marker/symbol line :: *</t>
+          <t>L1590: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="P156" s="1" t="inlineStr"/>
       <c r="Q156" s="1" t="inlineStr">
         <is>
-          <t>L1610: punctuation artifact: repeated periods :: Mchel Boulard...............</t>
+          <t>L1609: punctuation artifact: repeated periods :: . Joseph Panneton winter roads..</t>
         </is>
       </c>
       <c r="R156" s="1" t="inlineStr"/>
@@ -7750,18 +7462,18 @@
       <c r="M157" s="1" t="inlineStr"/>
       <c r="N157" s="1" t="inlineStr">
         <is>
-          <t>L837: symbol-only separator/garbage line :: $2760.20</t>
+          <t>L815: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O157" s="1" t="inlineStr">
         <is>
-          <t>L1594: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1591: symbol-only separator/garbage line | line starts with punctuation glued to text :: *38</t>
         </is>
       </c>
       <c r="P157" s="1" t="inlineStr"/>
       <c r="Q157" s="1" t="inlineStr">
         <is>
-          <t>L1613: punctuation artifact: repeated periods :: Leap) J......................</t>
+          <t>L1610: punctuation artifact: repeated periods :: Mchel Boulard...............</t>
         </is>
       </c>
       <c r="R157" s="1" t="inlineStr"/>
@@ -7789,18 +7501,18 @@
       <c r="M158" s="1" t="inlineStr"/>
       <c r="N158" s="1" t="inlineStr">
         <is>
-          <t>L841: isolated marker/symbol line :: 8</t>
+          <t>L825: symbol-only separator/garbage line :: 618, 60</t>
         </is>
       </c>
       <c r="O158" s="1" t="inlineStr">
         <is>
-          <t>L1596: symbol-only separator/garbage line :: 24,00</t>
+          <t>L1593: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="P158" s="1" t="inlineStr"/>
       <c r="Q158" s="1" t="inlineStr">
         <is>
-          <t>L1615: punctuation artifact: repeated periods :: Joseph Giroux ...............</t>
+          <t>L1613: punctuation artifact: repeated periods :: Leap) J......................</t>
         </is>
       </c>
       <c r="R158" s="1" t="inlineStr"/>
@@ -7828,18 +7540,18 @@
       <c r="M159" s="1" t="inlineStr"/>
       <c r="N159" s="1" t="inlineStr">
         <is>
-          <t>L842: isolated marker/symbol line :: å…”</t>
+          <t>L834: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O159" s="1" t="inlineStr">
         <is>
-          <t>L1597: isolated marker/symbol line :: 1</t>
+          <t>L1594: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P159" s="1" t="inlineStr"/>
       <c r="Q159" s="1" t="inlineStr">
         <is>
-          <t>L1616: punctuation artifact: repeated periods | suspicious token(s): LaBarre (odd internal casing) :: Deals to D, G. LaBarre Esq.,..</t>
+          <t>L1615: punctuation artifact: repeated periods :: Joseph Giroux ...............</t>
         </is>
       </c>
       <c r="R159" s="1" t="inlineStr"/>
@@ -7867,18 +7579,18 @@
       <c r="M160" s="1" t="inlineStr"/>
       <c r="N160" s="1" t="inlineStr">
         <is>
-          <t>L844: isolated marker/symbol line :: 3</t>
+          <t>L837: symbol-only separator/garbage line :: $2760.20</t>
         </is>
       </c>
       <c r="O160" s="1" t="inlineStr">
         <is>
-          <t>L1635: isolated marker/symbol line :: n</t>
+          <t>L1596: symbol-only separator/garbage line :: 24,00</t>
         </is>
       </c>
       <c r="P160" s="1" t="inlineStr"/>
       <c r="Q160" s="1" t="inlineStr">
         <is>
-          <t>L1619: punctuation artifact: repeated periods :: toise of stone .............</t>
+          <t>L1616: punctuation artifact: repeated periods | suspicious token(s): LaBarre (odd internal casing) :: Deals to D, G. LaBarre Esq.,..</t>
         </is>
       </c>
       <c r="R160" s="1" t="inlineStr"/>
@@ -7906,18 +7618,18 @@
       <c r="M161" s="1" t="inlineStr"/>
       <c r="N161" s="1" t="inlineStr">
         <is>
-          <t>L846: isolated marker/symbol line :: h</t>
+          <t>L841: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O161" s="1" t="inlineStr">
         <is>
-          <t>L1677: isolated marker/symbol line :: a.</t>
+          <t>L1597: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P161" s="1" t="inlineStr"/>
       <c r="Q161" s="1" t="inlineStr">
         <is>
-          <t>L1621: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoine DÃ©lorier 4 do.. ....</t>
+          <t>L1619: punctuation artifact: repeated periods :: toise of stone .............</t>
         </is>
       </c>
       <c r="R161" s="1" t="inlineStr"/>
@@ -7943,16 +7655,20 @@
       <c r="K162" s="1" t="inlineStr"/>
       <c r="L162" s="1" t="inlineStr"/>
       <c r="M162" s="1" t="inlineStr"/>
-      <c r="N162" s="1" t="inlineStr"/>
+      <c r="N162" s="1" t="inlineStr">
+        <is>
+          <t>L842: stray/suspicious non-ASCII glyph(s): U+5154 CJK UNIFIED IDEOGRAPH-5154 | isolated marker/symbol line :: 兔</t>
+        </is>
+      </c>
       <c r="O162" s="1" t="inlineStr">
         <is>
-          <t>L1679: symbol-only separator/garbage line :: 61,67</t>
+          <t>L1635: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="P162" s="1" t="inlineStr"/>
       <c r="Q162" s="1" t="inlineStr">
         <is>
-          <t>L1623: punctuation artifact: repeated periods :: Moise Matton wood ......</t>
+          <t>L1621: punctuation artifact: repeated periods :: Antoine Délorier 4 do.. ....</t>
         </is>
       </c>
       <c r="R162" s="1" t="inlineStr"/>
@@ -7978,16 +7694,20 @@
       <c r="K163" s="1" t="inlineStr"/>
       <c r="L163" s="1" t="inlineStr"/>
       <c r="M163" s="1" t="inlineStr"/>
-      <c r="N163" s="1" t="inlineStr"/>
+      <c r="N163" s="1" t="inlineStr">
+        <is>
+          <t>L844: isolated marker/symbol line :: 3</t>
+        </is>
+      </c>
       <c r="O163" s="1" t="inlineStr">
         <is>
-          <t>L1702: isolated marker/symbol line :: t</t>
+          <t>L1677: isolated marker/symbol line :: a.</t>
         </is>
       </c>
       <c r="P163" s="1" t="inlineStr"/>
       <c r="Q163" s="1" t="inlineStr">
         <is>
-          <t>L1634: punctuation artifact: repeated periods :: To Mr. Andrew Craik... 53,80</t>
+          <t>L1623: punctuation artifact: repeated periods :: Moise Matton wood ......</t>
         </is>
       </c>
       <c r="R163" s="1" t="inlineStr"/>
@@ -8013,14 +7733,22 @@
       <c r="K164" s="1" t="inlineStr"/>
       <c r="L164" s="1" t="inlineStr"/>
       <c r="M164" s="1" t="inlineStr"/>
-      <c r="N164" s="1" t="inlineStr"/>
+      <c r="N164" s="1" t="inlineStr">
+        <is>
+          <t>L846: isolated marker/symbol line :: h</t>
+        </is>
+      </c>
       <c r="O164" s="1" t="inlineStr">
         <is>
-          <t>L1704: isolated marker/symbol line | line starts with punctuation glued to text :: .J</t>
+          <t>L1679: symbol-only separator/garbage line :: 61,67</t>
         </is>
       </c>
       <c r="P164" s="1" t="inlineStr"/>
-      <c r="Q164" s="1" t="inlineStr"/>
+      <c r="Q164" s="1" t="inlineStr">
+        <is>
+          <t>L1634: punctuation artifact: repeated periods :: To Mr. Andrew Craik... 53,80</t>
+        </is>
+      </c>
       <c r="R164" s="1" t="inlineStr"/>
       <c r="S164" s="1" t="inlineStr"/>
       <c r="T164" s="1" t="inlineStr"/>
@@ -8047,7 +7775,7 @@
       <c r="N165" s="1" t="inlineStr"/>
       <c r="O165" s="1" t="inlineStr">
         <is>
-          <t>L1706: isolated marker/symbol line :: -</t>
+          <t>L1694: isolated marker/symbol line :: 9°</t>
         </is>
       </c>
       <c r="P165" s="1" t="inlineStr"/>
@@ -8061,6 +7789,99 @@
       <c r="X165" s="1" t="inlineStr"/>
       <c r="Y165" s="1" t="inlineStr"/>
     </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr"/>
+      <c r="B166" s="1" t="inlineStr"/>
+      <c r="C166" s="1" t="inlineStr"/>
+      <c r="D166" s="1" t="inlineStr"/>
+      <c r="E166" s="1" t="inlineStr"/>
+      <c r="F166" s="1" t="inlineStr"/>
+      <c r="G166" s="1" t="inlineStr"/>
+      <c r="H166" s="1" t="inlineStr"/>
+      <c r="I166" s="1" t="inlineStr"/>
+      <c r="J166" s="1" t="inlineStr"/>
+      <c r="K166" s="1" t="inlineStr"/>
+      <c r="L166" s="1" t="inlineStr"/>
+      <c r="M166" s="1" t="inlineStr"/>
+      <c r="N166" s="1" t="inlineStr"/>
+      <c r="O166" s="1" t="inlineStr">
+        <is>
+          <t>L1702: isolated marker/symbol line :: t</t>
+        </is>
+      </c>
+      <c r="P166" s="1" t="inlineStr"/>
+      <c r="Q166" s="1" t="inlineStr"/>
+      <c r="R166" s="1" t="inlineStr"/>
+      <c r="S166" s="1" t="inlineStr"/>
+      <c r="T166" s="1" t="inlineStr"/>
+      <c r="U166" s="1" t="inlineStr"/>
+      <c r="V166" s="1" t="inlineStr"/>
+      <c r="W166" s="1" t="inlineStr"/>
+      <c r="X166" s="1" t="inlineStr"/>
+      <c r="Y166" s="1" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr"/>
+      <c r="B167" s="1" t="inlineStr"/>
+      <c r="C167" s="1" t="inlineStr"/>
+      <c r="D167" s="1" t="inlineStr"/>
+      <c r="E167" s="1" t="inlineStr"/>
+      <c r="F167" s="1" t="inlineStr"/>
+      <c r="G167" s="1" t="inlineStr"/>
+      <c r="H167" s="1" t="inlineStr"/>
+      <c r="I167" s="1" t="inlineStr"/>
+      <c r="J167" s="1" t="inlineStr"/>
+      <c r="K167" s="1" t="inlineStr"/>
+      <c r="L167" s="1" t="inlineStr"/>
+      <c r="M167" s="1" t="inlineStr"/>
+      <c r="N167" s="1" t="inlineStr"/>
+      <c r="O167" s="1" t="inlineStr">
+        <is>
+          <t>L1704: isolated marker/symbol line | line starts with punctuation glued to text :: .J</t>
+        </is>
+      </c>
+      <c r="P167" s="1" t="inlineStr"/>
+      <c r="Q167" s="1" t="inlineStr"/>
+      <c r="R167" s="1" t="inlineStr"/>
+      <c r="S167" s="1" t="inlineStr"/>
+      <c r="T167" s="1" t="inlineStr"/>
+      <c r="U167" s="1" t="inlineStr"/>
+      <c r="V167" s="1" t="inlineStr"/>
+      <c r="W167" s="1" t="inlineStr"/>
+      <c r="X167" s="1" t="inlineStr"/>
+      <c r="Y167" s="1" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr"/>
+      <c r="B168" s="1" t="inlineStr"/>
+      <c r="C168" s="1" t="inlineStr"/>
+      <c r="D168" s="1" t="inlineStr"/>
+      <c r="E168" s="1" t="inlineStr"/>
+      <c r="F168" s="1" t="inlineStr"/>
+      <c r="G168" s="1" t="inlineStr"/>
+      <c r="H168" s="1" t="inlineStr"/>
+      <c r="I168" s="1" t="inlineStr"/>
+      <c r="J168" s="1" t="inlineStr"/>
+      <c r="K168" s="1" t="inlineStr"/>
+      <c r="L168" s="1" t="inlineStr"/>
+      <c r="M168" s="1" t="inlineStr"/>
+      <c r="N168" s="1" t="inlineStr"/>
+      <c r="O168" s="1" t="inlineStr">
+        <is>
+          <t>L1706: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
+      <c r="P168" s="1" t="inlineStr"/>
+      <c r="Q168" s="1" t="inlineStr"/>
+      <c r="R168" s="1" t="inlineStr"/>
+      <c r="S168" s="1" t="inlineStr"/>
+      <c r="T168" s="1" t="inlineStr"/>
+      <c r="U168" s="1" t="inlineStr"/>
+      <c r="V168" s="1" t="inlineStr"/>
+      <c r="W168" s="1" t="inlineStr"/>
+      <c r="X168" s="1" t="inlineStr"/>
+      <c r="Y168" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
